--- a/Gestion de proyectos practica/outputs/correccion-docente-2026-10-22/Flujo-de-caja-agrupado-VAN-TIR-corregido.xlsx
+++ b/Gestion de proyectos practica/outputs/correccion-docente-2026-10-22/Flujo-de-caja-agrupado-VAN-TIR-corregido.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo de caja" sheetId="1" r:id="R3ebbd16bcc9f4bf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan 12 meses" sheetId="2" r:id="Rcb71abc98dcb4553"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan comercial" sheetId="3" r:id="R290b868c09044f98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo de caja" sheetId="1" r:id="Rf8645ace330c4ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan 12 meses" sheetId="2" r:id="R3aaea0becafd43b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan comercial" sheetId="3" r:id="R5193ad010c0f4b46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cambios realizados" sheetId="4" r:id="R133b364554d14496"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Z_97E5A6E8_1452_495C_ADA9_7DBD435A0EEF_.wvu.FilterData" localSheetId="0" hidden="1">'Flujo de caja'!$A$2:$R$43</x:definedName>
@@ -38,7 +39,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="14">
+  <x:numFmts count="17">
     <x:numFmt numFmtId="164" formatCode="[$$]#,##0.00"/>
     <x:numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
     <x:numFmt numFmtId="166" formatCode="[&gt;=0.005]#,##0.00;[&lt;=-0.005](#,##0.00);&quot;-&quot;"/>
@@ -53,8 +54,11 @@
     <x:numFmt numFmtId="203" formatCode="#,##0"/>
     <x:numFmt numFmtId="204" formatCode="&quot;$&quot;#,##0"/>
     <x:numFmt numFmtId="205" formatCode="&quot;M&quot;0"/>
+    <x:numFmt numFmtId="206" formatCode="0.00"/>
+    <x:numFmt numFmtId="207" formatCode="0"/>
+    <x:numFmt numFmtId="208" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
   </x:numFmts>
-  <x:fonts count="26">
+  <x:fonts count="35">
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF000000"/>
@@ -214,8 +218,65 @@
       <x:name val="Arial"/>
       <x:scheme val="minor"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF262626"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF262626"/>
+      <x:name val="Arial"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF262626"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF262626"/>
+      <x:name val="Arial"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Arial"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF262626"/>
+      <x:name val="Arial"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="15"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF555555"/>
+      <x:name val="Arial"/>
+      <x:scheme val="minor"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="30">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -272,8 +333,98 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="18">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -409,11 +560,46 @@
         <x:color rgb="FFD9D9D9"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9EADBA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="295">
+  <x:cellXfs count="478">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
@@ -1188,6 +1374,555 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="13" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="8" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="26" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="8" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="26" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="28" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="28" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="28" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="28" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="8" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="8" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="28" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="30" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="30" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="29" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="27" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="29" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="29" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="29" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="29" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="32" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="32" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="8" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="26" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="26" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="26" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="26" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="8" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="8" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="26" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="26" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="8" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="26" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="26" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="8" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="30" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="30" fillId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="27" fillId="23" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="8" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="8" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="26" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="26" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="8" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="8" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="26" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="8" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="26" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="8" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="30" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="30" fillId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="27" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="25" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="28" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1611,7 +2346,7 @@
       </x:c>
       <x:c r="C4" s="213" t="n">
         <x:f>$C$53</x:f>
-        <x:v>300920.0943065033</x:v>
+        <x:v>228303.05555555553</x:v>
       </x:c>
       <x:c r="D4" s="213" t="n">
         <x:f t="shared" ref="D4:N4" si="1">0</x:f>
@@ -1659,7 +2394,7 @@
       </x:c>
       <x:c r="O4" s="213" t="n">
         <x:f>SUM(C4:N4)</x:f>
-        <x:v>300920.0943065033</x:v>
+        <x:v>228303.05555555553</x:v>
       </x:c>
       <x:c r="P4" s="213" t="n">
         <x:f>0</x:f>
@@ -1907,7 +2642,7 @@
       </x:c>
       <x:c r="C9" s="214" t="n">
         <x:f t="shared" ref="C9:N9" si="6">SUM(C4:C7)</x:f>
-        <x:v>300920.0943065033</x:v>
+        <x:v>228303.05555555553</x:v>
       </x:c>
       <x:c r="D9" s="214" t="n">
         <x:f t="shared" si="6">SUM(D4:D7)</x:f>
@@ -1955,7 +2690,7 @@
       </x:c>
       <x:c r="O9" s="214" t="n">
         <x:f>SUM(C9:N9)</x:f>
-        <x:v>300920.0943065033</x:v>
+        <x:v>228303.05555555553</x:v>
       </x:c>
       <x:c r="P9" s="214" t="n">
         <x:f t="shared" ref="P9:R9" si="7">SUM(P4:P7)</x:f>
@@ -2687,15 +3422,15 @@
       </x:c>
       <x:c r="K22" s="214" t="n">
         <x:f t="shared" si="23">SUM(K23:K27)</x:f>
-        <x:v>8456.666666666666</x:v>
+        <x:v>4844.444444444444</x:v>
       </x:c>
       <x:c r="L22" s="214" t="n">
         <x:f t="shared" si="23">SUM(L23:L27)</x:f>
-        <x:v>14798</x:v>
+        <x:v>9112.944444444445</x:v>
       </x:c>
       <x:c r="M22" s="214" t="n">
         <x:f t="shared" si="23">SUM(M23:M27)</x:f>
-        <x:v>4527.555555555557</x:v>
+        <x:v>3145.666666666667</x:v>
       </x:c>
       <x:c r="N22" s="214" t="n">
         <x:f t="shared" si="23">SUM(N23:N27)</x:f>
@@ -2703,19 +3438,19 @@
       </x:c>
       <x:c r="O22" s="214" t="n">
         <x:f>SUM(C22:N22)</x:f>
-        <x:v>27782.22222222222</x:v>
+        <x:v>17103.05555555556</x:v>
       </x:c>
       <x:c r="P22" s="214" t="n">
         <x:f t="shared" ref="P22:R22" si="24">SUM(P23:P27)</x:f>
-        <x:v>217247.11111111112</x:v>
+        <x:v>170403.33833333332</x:v>
       </x:c>
       <x:c r="Q22" s="214" t="n">
         <x:f t="shared" si="24">SUM(Q23:Q27)</x:f>
-        <x:v>821670.8888888889</x:v>
+        <x:v>640698.1472222222</x:v>
       </x:c>
       <x:c r="R22" s="215" t="n">
         <x:f t="shared" si="24">SUM(R23:R27)</x:f>
-        <x:v>1916319.6888888888</x:v>
+        <x:v>1497051.78</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="21" customHeight="1">
@@ -2758,12 +3493,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K23" s="213" t="n">
-        <x:f t="shared" si="25">$C$65/(1-$C$90)*$C$66*0.5</x:f>
-        <x:v>8456.666666666666</x:v>
+        <x:f t="shared" si="25">$C$65/(1-$C$90)*$L$83*0.5</x:f>
+        <x:v>4844.444444444444</x:v>
       </x:c>
       <x:c r="L23" s="213" t="n">
-        <x:f t="shared" si="25">$C$65/(1-$C$90)*$C$66*0.5</x:f>
-        <x:v>8456.666666666666</x:v>
+        <x:f t="shared" si="25">$C$65/(1-$C$90)*$L$83*0.5</x:f>
+        <x:v>4844.444444444444</x:v>
       </x:c>
       <x:c r="M23" s="213" t="n">
         <x:f t="shared" si="25">0</x:f>
@@ -2775,19 +3510,19 @@
       </x:c>
       <x:c r="O23" s="213" t="n">
         <x:f>SUM(C23:N23)</x:f>
-        <x:v>16913.333333333332</x:v>
+        <x:v>9688.888888888889</x:v>
       </x:c>
       <x:c r="P23" s="213" t="n">
         <x:f t="shared" ref="P23:R23" si="26">P132/(1-$C$90)*$C$66</x:f>
-        <x:v>38900.666666666664</x:v>
+        <x:v>26981.13333333333</x:v>
       </x:c>
       <x:c r="Q23" s="213" t="n">
         <x:f t="shared" si="26">Q132/(1-$C$90)*$C$66</x:f>
-        <x:v>143763.33333333334</x:v>
+        <x:v>98475.44444444444</x:v>
       </x:c>
       <x:c r="R23" s="213" t="n">
         <x:f t="shared" si="26">R132/(1-$C$90)*$C$66</x:f>
-        <x:v>299027.73333333334</x:v>
+        <x:v>204009.24444444443</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="21" customHeight="1">
@@ -2834,12 +3569,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L24" s="213" t="n">
-        <x:f t="shared" si="27">$C$65/(1-$C$90)*$C$67*0.6</x:f>
-        <x:v>6341.333333333334</x:v>
+        <x:f t="shared" si="27">$C$65/(1-$C$90)*$L$86*0.6</x:f>
+        <x:v>4268.5</x:v>
       </x:c>
       <x:c r="M24" s="213" t="n">
-        <x:f t="shared" si="27">$C$65/(1-$C$90)*$C$67*0.4</x:f>
-        <x:v>4227.555555555557</x:v>
+        <x:f t="shared" si="27">$C$65/(1-$C$90)*$L$86*0.4</x:f>
+        <x:v>2845.666666666667</x:v>
       </x:c>
       <x:c r="N24" s="213" t="n">
         <x:f t="shared" si="27">0</x:f>
@@ -2847,19 +3582,19 @@
       </x:c>
       <x:c r="O24" s="213" t="n">
         <x:f>SUM(C24:N24)</x:f>
-        <x:v>10568.88888888889</x:v>
+        <x:v>7114.166666666667</x:v>
       </x:c>
       <x:c r="P24" s="213" t="n">
         <x:f t="shared" ref="P24:R24" si="28">P132/(1-$C$90)*$C$67</x:f>
-        <x:v>24308.444444444445</x:v>
+        <x:v>18185.405000000002</x:v>
       </x:c>
       <x:c r="Q24" s="213" t="n">
         <x:f t="shared" si="28">Q132/(1-$C$90)*$C$67</x:f>
-        <x:v>89835.55555555556</x:v>
+        <x:v>66372.89166666668</x:v>
       </x:c>
       <x:c r="R24" s="213" t="n">
         <x:f t="shared" si="28">R132/(1-$C$90)*$C$67</x:f>
-        <x:v>186857.95555555556</x:v>
+        <x:v>137503.1466666667</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="21" customHeight="1">
@@ -2923,15 +3658,15 @@
       </x:c>
       <x:c r="P25" s="213" t="n">
         <x:f t="shared" ref="P25:R25" si="30">P132*$C$68/$C$65</x:f>
-        <x:v>690</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="Q25" s="213" t="n">
         <x:f t="shared" si="30">Q132*$C$68/$C$65</x:f>
-        <x:v>2550</x:v>
+        <x:v>2595</x:v>
       </x:c>
       <x:c r="R25" s="213" t="n">
         <x:f t="shared" si="30">R132*$C$68/$C$65</x:f>
-        <x:v>5304</x:v>
+        <x:v>5376</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="21" customHeight="1">
@@ -2942,51 +3677,51 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="C26" s="213" t="n">
-        <x:f t="shared" ref="C26:N26" si="31">C61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" ref="C26:N26" si="31">C61/(1-$C$90)*$C$69+C61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="213" t="n">
-        <x:f t="shared" si="31">D61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">D61/(1-$C$90)*$C$69+D61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E26" s="213" t="n">
-        <x:f t="shared" si="31">E61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">E61/(1-$C$90)*$C$69+E61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F26" s="213" t="n">
-        <x:f t="shared" si="31">F61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">F61/(1-$C$90)*$C$69+F61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G26" s="213" t="n">
-        <x:f t="shared" si="31">G61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">G61/(1-$C$90)*$C$69+G61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="213" t="n">
-        <x:f t="shared" si="31">H61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">H61/(1-$C$90)*$C$69+H61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I26" s="213" t="n">
-        <x:f t="shared" si="31">I61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">I61/(1-$C$90)*$C$69+I61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J26" s="213" t="n">
-        <x:f t="shared" si="31">J61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">J61/(1-$C$90)*$C$69+J61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K26" s="213" t="n">
-        <x:f t="shared" si="31">K61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">K61/(1-$C$90)*$C$69+K61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L26" s="213" t="n">
-        <x:f t="shared" si="31">L61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">L61/(1-$C$90)*$C$69+L61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M26" s="213" t="n">
-        <x:f t="shared" si="31">M61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">M61/(1-$C$90)*$C$69+M61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N26" s="213" t="n">
-        <x:f t="shared" si="31">N61*SUM($C$69:$C$70)</x:f>
+        <x:f t="shared" si="31">N61/(1-$C$90)*$C$69+N61*$C$70</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O26" s="213" t="n">
@@ -2994,16 +3729,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P26" s="213" t="n">
-        <x:f t="shared" ref="P26:R26" si="32">P61*SUM($C$69:$C$70)</x:f>
-        <x:v>130680</x:v>
+        <x:f t="shared" ref="P26:R26" si="32">P61/(1-$C$90)*$C$69+P61*$C$70</x:f>
+        <x:v>101857.8</x:v>
       </x:c>
       <x:c r="Q26" s="213" t="n">
-        <x:f t="shared" si="32">Q61*SUM($C$69:$C$70)</x:f>
-        <x:v>509020</x:v>
+        <x:f t="shared" si="32">Q61/(1-$C$90)*$C$69+Q61*$C$70</x:f>
+        <x:v>396752.8111111111</x:v>
       </x:c>
       <x:c r="R26" s="213" t="n">
-        <x:f t="shared" si="32">R61*SUM($C$69:$C$70)</x:f>
-        <x:v>1246700</x:v>
+        <x:f t="shared" si="32">R61/(1-$C$90)*$C$69+R61*$C$70</x:f>
+        <x:v>971733.3888888889</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="21" customHeight="1">
@@ -3080,7 +3815,7 @@
     </x:row>
     <x:row r="28" ht="21" customHeight="1">
       <x:c r="A28" s="198" t="str">
-        <x:v>Equipo y servicios de desarrollo</x:v>
+        <x:v>Equipo, servicios, onboarding y soporte</x:v>
       </x:c>
       <x:c r="B28" s="199" t="str">
         <x:v>USD</x:v>
@@ -3139,15 +3874,15 @@
       </x:c>
       <x:c r="P28" s="214" t="n">
         <x:f t="shared" ref="P28:R28" si="36">SUM(P29:P37)</x:f>
-        <x:v>15528.288191304466</x:v>
+        <x:v>18978.288191304466</x:v>
       </x:c>
       <x:c r="Q28" s="214" t="n">
         <x:f t="shared" si="36">SUM(Q29:Q37)</x:f>
-        <x:v>43116.58389297663</x:v>
+        <x:v>50241.58389297663</x:v>
       </x:c>
       <x:c r="R28" s="215" t="n">
         <x:f t="shared" si="36">SUM(R29:R37)</x:f>
-        <x:v>96905.69103879345</x:v>
+        <x:v>108305.69103879345</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="21" customHeight="1">
@@ -3656,7 +4391,7 @@
     </x:row>
     <x:row r="36" ht="21" customHeight="1">
       <x:c r="A36" s="200" t="str">
-        <x:v>Coordinación y documentación (incluida en FTE)</x:v>
+        <x:v>Onboarding de médicos y clínicas</x:v>
       </x:c>
       <x:c r="B36" s="196" t="str">
         <x:v>USD</x:v>
@@ -3714,16 +4449,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="P36" s="213" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>'Plan comercial'!C65</x:f>
+        <x:v>3450</x:v>
       </x:c>
       <x:c r="Q36" s="213" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>'Plan comercial'!D65</x:f>
+        <x:v>7125</x:v>
       </x:c>
       <x:c r="R36" s="213" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
+        <x:f>'Plan comercial'!E65</x:f>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="21" customHeight="1">
@@ -4055,15 +4790,15 @@
       </x:c>
       <x:c r="K41" s="216" t="n">
         <x:f t="shared" si="55">SUM(K12,K17,K22,K28,K38)</x:f>
-        <x:v>25656.666666666664</x:v>
+        <x:v>22044.444444444445</x:v>
       </x:c>
       <x:c r="L41" s="216" t="n">
         <x:f t="shared" si="55">SUM(L12,L17,L22,L28,L38)</x:f>
-        <x:v>33498</x:v>
+        <x:v>27812.944444444445</x:v>
       </x:c>
       <x:c r="M41" s="216" t="n">
         <x:f t="shared" si="55">SUM(M12,M17,M22,M28,M38)</x:f>
-        <x:v>18227.555555555555</x:v>
+        <x:v>16845.666666666668</x:v>
       </x:c>
       <x:c r="N41" s="216" t="n">
         <x:f t="shared" si="55">SUM(N12,N17,N22,N28,N38)</x:f>
@@ -4071,19 +4806,19 @@
       </x:c>
       <x:c r="O41" s="216" t="n">
         <x:f>SUM(C41:N41)</x:f>
-        <x:v>238982.22222222222</x:v>
+        <x:v>228303.05555555553</x:v>
       </x:c>
       <x:c r="P41" s="216" t="n">
         <x:f t="shared" ref="P41:R41" si="56">SUM(P12,P17,P22,P28,P38)</x:f>
-        <x:v>310775.39930241555</x:v>
+        <x:v>267381.6265246378</x:v>
       </x:c>
       <x:c r="Q41" s="216" t="n">
         <x:f t="shared" si="56">SUM(Q12,Q17,Q22,Q28,Q38)</x:f>
-        <x:v>990787.4727818655</x:v>
+        <x:v>816939.7311151988</x:v>
       </x:c>
       <x:c r="R41" s="217" t="n">
         <x:f t="shared" si="56">SUM(R12,R17,R22,R28,R38)</x:f>
-        <x:v>2187225.379927682</x:v>
+        <x:v>1779357.4710387934</x:v>
       </x:c>
       <x:c r="S41" s="17"/>
       <x:c r="T41" s="17"/>
@@ -4104,7 +4839,7 @@
       </x:c>
       <x:c r="C42" s="218" t="n">
         <x:f t="shared" ref="C42:N42" si="57">C9-C41</x:f>
-        <x:v>285220.0943065033</x:v>
+        <x:v>212603.05555555553</x:v>
       </x:c>
       <x:c r="D42" s="218" t="n">
         <x:f t="shared" si="57">D9-D41</x:f>
@@ -4136,15 +4871,15 @@
       </x:c>
       <x:c r="K42" s="218" t="n">
         <x:f t="shared" si="57">K9-K41</x:f>
-        <x:v>-25656.666666666664</x:v>
+        <x:v>-22044.444444444445</x:v>
       </x:c>
       <x:c r="L42" s="218" t="n">
         <x:f t="shared" si="57">L9-L41</x:f>
-        <x:v>-33498</x:v>
+        <x:v>-27812.944444444445</x:v>
       </x:c>
       <x:c r="M42" s="218" t="n">
         <x:f t="shared" si="57">M9-M41</x:f>
-        <x:v>-18227.555555555555</x:v>
+        <x:v>-16845.666666666668</x:v>
       </x:c>
       <x:c r="N42" s="218" t="n">
         <x:f t="shared" si="57">N9-N41</x:f>
@@ -4152,19 +4887,19 @@
       </x:c>
       <x:c r="O42" s="218" t="n">
         <x:f>SUM(C42:N42)</x:f>
-        <x:v>61937.87208428109</x:v>
+        <x:v>-2.546585164964199e-11</x:v>
       </x:c>
       <x:c r="P42" s="218" t="n">
         <x:f t="shared" ref="P42:R42" si="58">P9-P41</x:f>
-        <x:v>-27425.39930241555</x:v>
+        <x:v>15968.373475362197</x:v>
       </x:c>
       <x:c r="Q42" s="218" t="n">
         <x:f t="shared" si="58">Q9-Q41</x:f>
-        <x:v>-34512.47278186551</x:v>
+        <x:v>139335.2688848012</x:v>
       </x:c>
       <x:c r="R42" s="218" t="n">
         <x:f t="shared" si="58">R9-R41</x:f>
-        <x:v>43149.620072317775</x:v>
+        <x:v>451017.52896120655</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="21" customHeight="1">
@@ -4176,67 +4911,67 @@
       </x:c>
       <x:c r="C43" s="219" t="n">
         <x:f>C42</x:f>
-        <x:v>285220.0943065033</x:v>
+        <x:v>212603.05555555553</x:v>
       </x:c>
       <x:c r="D43" s="219" t="n">
         <x:f t="shared" ref="D43:N43" si="59">C43+D42</x:f>
-        <x:v>268220.0943065033</x:v>
+        <x:v>195603.05555555553</x:v>
       </x:c>
       <x:c r="E43" s="219" t="n">
         <x:f t="shared" si="59">D43+E42</x:f>
-        <x:v>253020.0943065033</x:v>
+        <x:v>180403.05555555553</x:v>
       </x:c>
       <x:c r="F43" s="219" t="n">
         <x:f t="shared" si="59">E43+F42</x:f>
-        <x:v>233020.0943065033</x:v>
+        <x:v>160403.05555555553</x:v>
       </x:c>
       <x:c r="G43" s="219" t="n">
         <x:f t="shared" si="59">F43+G42</x:f>
-        <x:v>216820.0943065033</x:v>
+        <x:v>144203.05555555553</x:v>
       </x:c>
       <x:c r="H43" s="219" t="n">
         <x:f t="shared" si="59">G43+H42</x:f>
-        <x:v>199420.0943065033</x:v>
+        <x:v>126803.05555555553</x:v>
       </x:c>
       <x:c r="I43" s="219" t="n">
         <x:f t="shared" si="59">H43+I42</x:f>
-        <x:v>180220.0943065033</x:v>
+        <x:v>107603.05555555553</x:v>
       </x:c>
       <x:c r="J43" s="219" t="n">
         <x:f t="shared" si="59">I43+J42</x:f>
-        <x:v>159820.0943065033</x:v>
+        <x:v>87203.05555555553</x:v>
       </x:c>
       <x:c r="K43" s="219" t="n">
         <x:f t="shared" si="59">J43+K42</x:f>
-        <x:v>134163.42763983665</x:v>
+        <x:v>65158.61111111109</x:v>
       </x:c>
       <x:c r="L43" s="219" t="n">
         <x:f t="shared" si="59">K43+L42</x:f>
-        <x:v>100665.42763983665</x:v>
+        <x:v>37345.66666666664</x:v>
       </x:c>
       <x:c r="M43" s="219" t="n">
         <x:f t="shared" si="59">L43+M42</x:f>
-        <x:v>82437.87208428109</x:v>
+        <x:v>20499.999999999975</x:v>
       </x:c>
       <x:c r="N43" s="219" t="n">
         <x:f t="shared" si="59">M43+N42</x:f>
-        <x:v>61937.87208428109</x:v>
+        <x:v>-2.546585164964199e-11</x:v>
       </x:c>
       <x:c r="O43" s="219" t="n">
         <x:f>N43</x:f>
-        <x:v>61937.87208428109</x:v>
+        <x:v>-2.546585164964199e-11</x:v>
       </x:c>
       <x:c r="P43" s="219" t="n">
         <x:f>N43+P42</x:f>
-        <x:v>34512.47278186554</x:v>
+        <x:v>15968.373475362172</x:v>
       </x:c>
       <x:c r="Q43" s="219" t="n">
         <x:f t="shared" ref="Q43:R43" si="60">P43+Q42</x:f>
-        <x:v>2.9103830456733704e-11</x:v>
+        <x:v>155303.64236016336</x:v>
       </x:c>
       <x:c r="R43" s="219" t="n">
         <x:f t="shared" si="60">Q43+R42</x:f>
-        <x:v>43149.620072317804</x:v>
+        <x:v>606321.1713213699</x:v>
       </x:c>
       <x:c r="S43" s="27"/>
       <x:c r="T43" s="27"/>
@@ -4309,15 +5044,15 @@
       </x:c>
       <x:c r="K45" s="221" t="n">
         <x:f t="shared" si="61">SUM(K5:K7)-K41</x:f>
-        <x:v>-25656.666666666664</x:v>
+        <x:v>-22044.444444444445</x:v>
       </x:c>
       <x:c r="L45" s="221" t="n">
         <x:f t="shared" si="61">SUM(L5:L7)-L41</x:f>
-        <x:v>-33498</x:v>
+        <x:v>-27812.944444444445</x:v>
       </x:c>
       <x:c r="M45" s="221" t="n">
         <x:f t="shared" si="61">SUM(M5:M7)-M41</x:f>
-        <x:v>-18227.555555555555</x:v>
+        <x:v>-16845.666666666668</x:v>
       </x:c>
       <x:c r="N45" s="221" t="n">
         <x:f t="shared" si="61">SUM(N5:N7)-N41</x:f>
@@ -4325,19 +5060,19 @@
       </x:c>
       <x:c r="O45" s="221" t="n">
         <x:f>SUM(C45:N45)</x:f>
-        <x:v>-238982.22222222222</x:v>
+        <x:v>-228303.05555555553</x:v>
       </x:c>
       <x:c r="P45" s="221" t="n">
         <x:f t="shared" ref="P45:R45" si="62">SUM(P5:P7)-P41</x:f>
-        <x:v>-27425.39930241555</x:v>
+        <x:v>15968.373475362197</x:v>
       </x:c>
       <x:c r="Q45" s="221" t="n">
         <x:f t="shared" si="62">SUM(Q5:Q7)-Q41</x:f>
-        <x:v>-34512.47278186551</x:v>
+        <x:v>139335.2688848012</x:v>
       </x:c>
       <x:c r="R45" s="221" t="n">
         <x:f t="shared" si="62">SUM(R5:R7)-R41</x:f>
-        <x:v>43149.620072317775</x:v>
+        <x:v>451017.52896120655</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="21" customHeight="1">
@@ -4381,35 +5116,35 @@
       </x:c>
       <x:c r="K46" s="221" t="n">
         <x:f t="shared" si="63">J46+K45</x:f>
-        <x:v>-166756.66666666666</x:v>
+        <x:v>-163144.44444444444</x:v>
       </x:c>
       <x:c r="L46" s="221" t="n">
         <x:f t="shared" si="63">K46+L45</x:f>
-        <x:v>-200254.66666666666</x:v>
+        <x:v>-190957.38888888888</x:v>
       </x:c>
       <x:c r="M46" s="221" t="n">
         <x:f t="shared" si="63">L46+M45</x:f>
-        <x:v>-218482.22222222222</x:v>
+        <x:v>-207803.05555555553</x:v>
       </x:c>
       <x:c r="N46" s="221" t="n">
         <x:f t="shared" si="63">M46+N45</x:f>
-        <x:v>-238982.22222222222</x:v>
+        <x:v>-228303.05555555553</x:v>
       </x:c>
       <x:c r="O46" s="221" t="n">
         <x:f>N46</x:f>
-        <x:v>-238982.22222222222</x:v>
+        <x:v>-228303.05555555553</x:v>
       </x:c>
       <x:c r="P46" s="221" t="n">
         <x:f>N46+P45</x:f>
-        <x:v>-266407.6215246378</x:v>
+        <x:v>-212334.68208019334</x:v>
       </x:c>
       <x:c r="Q46" s="221" t="n">
         <x:f t="shared" ref="Q46:R46" si="64">P46+Q45</x:f>
-        <x:v>-300920.0943065033</x:v>
+        <x:v>-72999.41319539215</x:v>
       </x:c>
       <x:c r="R46" s="221" t="n">
         <x:f t="shared" si="64">Q46+R45</x:f>
-        <x:v>-257770.47423418553</x:v>
+        <x:v>378018.11576581444</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="21" customHeight="1">
@@ -4472,7 +5207,7 @@
       <x:c r="F49" s="221" t="str"/>
       <x:c r="G49" s="221" t="n">
         <x:f>XNPV(C153,G166:G181,F166:F181)</x:f>
-        <x:v>-233388.96863044554</x:v>
+        <x:v>103250.74054501748</x:v>
       </x:c>
       <x:c r="H49" s="220"/>
       <x:c r="I49" s="220"/>
@@ -4495,16 +5230,16 @@
       </x:c>
       <x:c r="C50" s="220" t="n">
         <x:f>SUM(O41:R41)</x:f>
-        <x:v>3727770.4742341856</x:v>
+        <x:v>3091981.8842341853</x:v>
       </x:c>
       <x:c r="D50" s="220"/>
       <x:c r="E50" s="221" t="str">
         <x:v>TIR anual</x:v>
       </x:c>
       <x:c r="F50" s="221"/>
-      <x:c r="G50" s="221" t="str">
+      <x:c r="G50" s="221" t="n">
         <x:f>IF(C51&lt;0,"No determinada",XIRR(G166:G181,F166:F181))</x:f>
-        <x:v>No determinada</x:v>
+        <x:v>0.36829809694647936</x:v>
       </x:c>
       <x:c r="H50" s="220"/>
       <x:c r="I50" s="220"/>
@@ -4527,7 +5262,7 @@
       </x:c>
       <x:c r="C51" s="220" t="n">
         <x:f>SUM(O45:R45)</x:f>
-        <x:v>-257770.47423418553</x:v>
+        <x:v>378018.11576581444</x:v>
       </x:c>
       <x:c r="D51" s="220"/>
       <x:c r="E51" s="221" t="str">
@@ -4559,7 +5294,7 @@
       </x:c>
       <x:c r="C52" s="221" t="n">
         <x:f>MAX(0,-MIN(C46:N46,P46:R46))</x:f>
-        <x:v>300920.0943065033</x:v>
+        <x:v>228303.05555555553</x:v>
       </x:c>
       <x:c r="D52" s="221"/>
       <x:c r="E52" s="221" t="str">
@@ -4591,7 +5326,7 @@
       </x:c>
       <x:c r="C53" s="220" t="n">
         <x:f>C52+C97</x:f>
-        <x:v>300920.0943065033</x:v>
+        <x:v>228303.05555555553</x:v>
       </x:c>
       <x:c r="D53" s="220"/>
       <x:c r="E53" s="220" t="str">
@@ -4623,7 +5358,7 @@
       </x:c>
       <x:c r="C54" s="221" t="n">
         <x:f>R43</x:f>
-        <x:v>43149.620072317804</x:v>
+        <x:v>606321.1713213699</x:v>
       </x:c>
       <x:c r="D54" s="221"/>
       <x:c r="E54" s="221" t="str">
@@ -4654,7 +5389,7 @@
       </x:c>
       <x:c r="C55" s="220" t="n">
         <x:f>O41</x:f>
-        <x:v>238982.22222222222</x:v>
+        <x:v>228303.05555555553</x:v>
       </x:c>
       <x:c r="D55" s="220"/>
       <x:c r="E55" s="220"/>
@@ -5017,37 +5752,89 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="P62" s="225" t="n">
-        <x:f>N62+P132-P59</x:f>
+        <x:f>N62+P132-P59-P135</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="Q62" s="225" t="n">
-        <x:f t="shared" ref="Q62:R62" si="72">P62+Q132-Q59</x:f>
+        <x:f t="shared" ref="Q62:R62" si="72">P62+Q132-Q59-Q135</x:f>
         <x:v>80</x:v>
       </x:c>
       <x:c r="R62" s="225" t="n">
-        <x:f t="shared" si="72">Q62+R132-R59</x:f>
+        <x:f t="shared" si="72">Q62+R132-R59-R135</x:f>
         <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="21" customHeight="1">
-      <x:c r="A63" s="196"/>
-      <x:c r="B63" s="196"/>
-      <x:c r="C63" s="208"/>
-      <x:c r="D63" s="208"/>
-      <x:c r="E63" s="208"/>
-      <x:c r="F63" s="208"/>
-      <x:c r="G63" s="208"/>
-      <x:c r="H63" s="208"/>
-      <x:c r="I63" s="208"/>
-      <x:c r="J63" s="208"/>
-      <x:c r="K63" s="208"/>
-      <x:c r="L63" s="208"/>
-      <x:c r="M63" s="208"/>
-      <x:c r="N63" s="208"/>
-      <x:c r="O63" s="226"/>
-      <x:c r="P63" s="226"/>
-      <x:c r="Q63" s="226"/>
-      <x:c r="R63" s="226"/>
+      <x:c r="A63" s="446" t="str">
+        <x:v>Kits demostradores entregados a clínicas</x:v>
+      </x:c>
+      <x:c r="B63" s="446" t="str">
+        <x:v>unidades</x:v>
+      </x:c>
+      <x:c r="C63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N63" s="447" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O63" s="448" t="n">
+        <x:f>SUM(C63:N63)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P63" s="448" t="n">
+        <x:f>P135</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q63" s="448" t="n">
+        <x:f>Q135</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="R63" s="448" t="n">
+        <x:f>R135</x:f>
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="21" customHeight="1">
       <x:c r="A64" s="198" t="str">
@@ -5056,18 +5843,24 @@
       <x:c r="B64" s="199"/>
       <x:c r="C64" s="227"/>
       <x:c r="D64" s="227"/>
-      <x:c r="E64" s="227"/>
-      <x:c r="F64" s="227"/>
-      <x:c r="G64" s="227"/>
+      <x:c r="E64" s="435" t="str">
+        <x:v>Costos unitarios trazables</x:v>
+      </x:c>
+      <x:c r="F64" s="436"/>
+      <x:c r="G64" s="437"/>
       <x:c r="H64" s="227"/>
       <x:c r="I64" s="227"/>
-      <x:c r="J64" s="227"/>
-      <x:c r="K64" s="227"/>
-      <x:c r="L64" s="227"/>
+      <x:c r="J64" s="435" t="str">
+        <x:v>Importación simplificada por kit</x:v>
+      </x:c>
+      <x:c r="K64" s="436"/>
+      <x:c r="L64" s="437"/>
       <x:c r="M64" s="227"/>
-      <x:c r="N64" s="227"/>
-      <x:c r="O64" s="228"/>
-      <x:c r="P64" s="228"/>
+      <x:c r="N64" s="435" t="str">
+        <x:v>Consultas especializadas</x:v>
+      </x:c>
+      <x:c r="O64" s="436"/>
+      <x:c r="P64" s="437"/>
       <x:c r="Q64" s="228"/>
       <x:c r="R64" s="229"/>
     </x:row>
@@ -5078,48 +5871,87 @@
       <x:c r="B65" s="196" t="str">
         <x:v>unidades</x:v>
       </x:c>
-      <x:c r="C65" s="230" t="n">
+      <x:c r="C65" s="428" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D65" s="208"/>
-      <x:c r="E65" s="208"/>
-      <x:c r="F65" s="208"/>
-      <x:c r="G65" s="208"/>
+      <x:c r="E65" s="308" t="str">
+        <x:v>Lector: materiales y procesos</x:v>
+      </x:c>
+      <x:c r="F65" s="308" t="str">
+        <x:v>USD/u</x:v>
+      </x:c>
+      <x:c r="G65" s="440" t="n">
+        <x:v>49.3</x:v>
+      </x:c>
       <x:c r="H65" s="208"/>
       <x:c r="I65" s="208"/>
-      <x:c r="J65" s="208"/>
-      <x:c r="K65" s="208"/>
-      <x:c r="L65" s="208"/>
+      <x:c r="J65" s="308" t="str">
+        <x:v>Lector ensamblado importado</x:v>
+      </x:c>
+      <x:c r="K65" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L65" s="313" t="n">
+        <x:f>SUM(G65,G71)</x:f>
+        <x:v>55.379999999999995</x:v>
+      </x:c>
       <x:c r="M65" s="208"/>
-      <x:c r="N65" s="208"/>
-      <x:c r="O65" s="226"/>
-      <x:c r="P65" s="226"/>
+      <x:c r="N65" s="308" t="str">
+        <x:v>Médicas</x:v>
+      </x:c>
+      <x:c r="O65" s="323" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="P65" s="445" t="n">
+        <x:v>3000</x:v>
+      </x:c>
       <x:c r="Q65" s="226"/>
       <x:c r="R65" s="226"/>
     </x:row>
     <x:row r="66" ht="21" customHeight="1">
       <x:c r="A66" s="196" t="str">
-        <x:v>Costo de fabricación por kit</x:v>
+        <x:v>Costo directo de fabricación por kit</x:v>
       </x:c>
       <x:c r="B66" s="196" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="C66" s="231" t="n">
-        <x:v>152.22</x:v>
+      <x:c r="C66" s="297" t="n">
+        <x:f>G85</x:f>
+        <x:v>102.46</x:v>
       </x:c>
       <x:c r="D66" s="208"/>
-      <x:c r="E66" s="208"/>
-      <x:c r="F66" s="208"/>
-      <x:c r="G66" s="208"/>
+      <x:c r="E66" s="308" t="str">
+        <x:v>Lector: armado e inspección</x:v>
+      </x:c>
+      <x:c r="F66" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G66" s="441" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="H66" s="208"/>
       <x:c r="I66" s="208"/>
-      <x:c r="J66" s="208"/>
-      <x:c r="K66" s="208"/>
-      <x:c r="L66" s="208"/>
+      <x:c r="J66" s="308" t="str">
+        <x:v>Pulsera ensamblada importada</x:v>
+      </x:c>
+      <x:c r="K66" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L66" s="313" t="n">
+        <x:f>SUM(G72,G78)</x:f>
+        <x:v>31.75</x:v>
+      </x:c>
       <x:c r="M66" s="208"/>
-      <x:c r="N66" s="208"/>
-      <x:c r="O66" s="226"/>
-      <x:c r="P66" s="226"/>
+      <x:c r="N66" s="308" t="str">
+        <x:v>Legales</x:v>
+      </x:c>
+      <x:c r="O66" s="323" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="P66" s="445" t="n">
+        <x:v>2500</x:v>
+      </x:c>
       <x:c r="Q66" s="226"/>
       <x:c r="R66" s="226"/>
     </x:row>
@@ -5130,22 +5962,42 @@
       <x:c r="B67" s="196" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="C67" s="231" t="n">
-        <x:v>95.12</x:v>
+      <x:c r="C67" s="297" t="n">
+        <x:f>L78</x:f>
+        <x:v>69.05850000000001</x:v>
       </x:c>
       <x:c r="D67" s="208"/>
-      <x:c r="E67" s="208"/>
-      <x:c r="F67" s="208"/>
-      <x:c r="G67" s="208"/>
+      <x:c r="E67" s="308" t="str">
+        <x:v>Lector: programación</x:v>
+      </x:c>
+      <x:c r="F67" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G67" s="441" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="H67" s="208"/>
       <x:c r="I67" s="208"/>
-      <x:c r="J67" s="208"/>
-      <x:c r="K67" s="208"/>
-      <x:c r="L67" s="208"/>
+      <x:c r="J67" s="317" t="str">
+        <x:v>Valor importado total</x:v>
+      </x:c>
+      <x:c r="K67" s="317" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L67" s="318" t="n">
+        <x:f>SUM(L65:L66)</x:f>
+        <x:v>87.13</x:v>
+      </x:c>
       <x:c r="M67" s="208"/>
-      <x:c r="N67" s="208"/>
-      <x:c r="O67" s="226"/>
-      <x:c r="P67" s="226"/>
+      <x:c r="N67" s="308" t="str">
+        <x:v>Regulatorias</x:v>
+      </x:c>
+      <x:c r="O67" s="323" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="P67" s="445" t="n">
+        <x:v>3500</x:v>
+      </x:c>
       <x:c r="Q67" s="226"/>
       <x:c r="R67" s="226"/>
     </x:row>
@@ -5156,48 +6008,86 @@
       <x:c r="B68" s="196" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="C68" s="231" t="n">
+      <x:c r="C68" s="429" t="n">
         <x:v>300</x:v>
       </x:c>
       <x:c r="D68" s="208"/>
-      <x:c r="E68" s="208"/>
-      <x:c r="F68" s="208"/>
-      <x:c r="G68" s="208"/>
+      <x:c r="E68" s="308" t="str">
+        <x:v>Lector: prueba funcional</x:v>
+      </x:c>
+      <x:c r="F68" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G68" s="441" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="H68" s="208"/>
       <x:c r="I68" s="208"/>
-      <x:c r="J68" s="208"/>
-      <x:c r="K68" s="208"/>
-      <x:c r="L68" s="208"/>
+      <x:c r="J68" s="308" t="str">
+        <x:v>Flete internacional</x:v>
+      </x:c>
+      <x:c r="K68" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L68" s="440" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="M68" s="208"/>
-      <x:c r="N68" s="208"/>
-      <x:c r="O68" s="226"/>
-      <x:c r="P68" s="226"/>
+      <x:c r="N68" s="308" t="str">
+        <x:v>Contables e impositivas</x:v>
+      </x:c>
+      <x:c r="O68" s="323" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="P68" s="445" t="n">
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="Q68" s="226"/>
       <x:c r="R68" s="226"/>
     </x:row>
     <x:row r="69" ht="21" customHeight="1">
       <x:c r="A69" s="196" t="str">
-        <x:v>Fabricación por parche de recambio</x:v>
+        <x:v>Fabricación directa por parche de recambio</x:v>
       </x:c>
       <x:c r="B69" s="196" t="str">
         <x:v>USD/parche</x:v>
       </x:c>
-      <x:c r="C69" s="231" t="n">
-        <x:v>17</x:v>
+      <x:c r="C69" s="297" t="n">
+        <x:f>G86</x:f>
+        <x:v>11.33</x:v>
       </x:c>
       <x:c r="D69" s="208"/>
-      <x:c r="E69" s="208"/>
-      <x:c r="F69" s="208"/>
-      <x:c r="G69" s="208"/>
+      <x:c r="E69" s="308" t="str">
+        <x:v>Lector: registro y trazabilidad</x:v>
+      </x:c>
+      <x:c r="F69" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G69" s="441" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="H69" s="208"/>
       <x:c r="I69" s="208"/>
-      <x:c r="J69" s="208"/>
-      <x:c r="K69" s="208"/>
-      <x:c r="L69" s="208"/>
+      <x:c r="J69" s="308" t="str">
+        <x:v>Seguro</x:v>
+      </x:c>
+      <x:c r="K69" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L69" s="440" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M69" s="208"/>
-      <x:c r="N69" s="208"/>
-      <x:c r="O69" s="226"/>
-      <x:c r="P69" s="226"/>
+      <x:c r="N69" s="319" t="str">
+        <x:v>Total consultas</x:v>
+      </x:c>
+      <x:c r="O69" s="329" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="P69" s="330" t="n">
+        <x:f>SUM(P65:P68)</x:f>
+        <x:v>10000</x:v>
+      </x:c>
       <x:c r="Q69" s="226"/>
       <x:c r="R69" s="226"/>
     </x:row>
@@ -5208,18 +6098,32 @@
       <x:c r="B70" s="196" t="str">
         <x:v>USD/parche</x:v>
       </x:c>
-      <x:c r="C70" s="231" t="n">
+      <x:c r="C70" s="429" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D70" s="208"/>
-      <x:c r="E70" s="208"/>
-      <x:c r="F70" s="208"/>
-      <x:c r="G70" s="208"/>
+      <x:c r="E70" s="308" t="str">
+        <x:v>Lector: total</x:v>
+      </x:c>
+      <x:c r="F70" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G70" s="316" t="n">
+        <x:f>SUM(G66:G69)</x:f>
+        <x:v>25</x:v>
+      </x:c>
       <x:c r="H70" s="208"/>
       <x:c r="I70" s="208"/>
-      <x:c r="J70" s="208"/>
-      <x:c r="K70" s="208"/>
-      <x:c r="L70" s="208"/>
+      <x:c r="J70" s="317" t="str">
+        <x:v>CIF</x:v>
+      </x:c>
+      <x:c r="K70" s="317" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L70" s="318" t="n">
+        <x:f>SUM(L67:L69)</x:f>
+        <x:v>100.13</x:v>
+      </x:c>
       <x:c r="M70" s="208"/>
       <x:c r="N70" s="208"/>
       <x:c r="O70" s="226"/>
@@ -5238,14 +6142,27 @@
         <x:v>3500000</x:v>
       </x:c>
       <x:c r="D71" s="208"/>
-      <x:c r="E71" s="208"/>
-      <x:c r="F71" s="208"/>
-      <x:c r="G71" s="208"/>
+      <x:c r="E71" s="308" t="str">
+        <x:v>Lector: mano de obra</x:v>
+      </x:c>
+      <x:c r="F71" s="308" t="str">
+        <x:v>USD/u</x:v>
+      </x:c>
+      <x:c r="G71" s="313" t="n">
+        <x:f>ROUND(G70/60*$C$80,2)</x:f>
+        <x:v>6.08</x:v>
+      </x:c>
       <x:c r="H71" s="208"/>
       <x:c r="I71" s="208"/>
-      <x:c r="J71" s="208"/>
-      <x:c r="K71" s="208"/>
-      <x:c r="L71" s="208"/>
+      <x:c r="J71" s="308" t="str">
+        <x:v>Derecho estimado</x:v>
+      </x:c>
+      <x:c r="K71" s="308" t="str">
+        <x:v>% CIF</x:v>
+      </x:c>
+      <x:c r="L71" s="443" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
       <x:c r="M71" s="208"/>
       <x:c r="N71" s="208"/>
       <x:c r="O71" s="226"/>
@@ -5264,14 +6181,26 @@
         <x:v>2500000</x:v>
       </x:c>
       <x:c r="D72" s="208"/>
-      <x:c r="E72" s="208"/>
-      <x:c r="F72" s="208"/>
-      <x:c r="G72" s="208"/>
+      <x:c r="E72" s="308" t="str">
+        <x:v>Pulsera: materiales y procesos</x:v>
+      </x:c>
+      <x:c r="F72" s="308" t="str">
+        <x:v>USD/u</x:v>
+      </x:c>
+      <x:c r="G72" s="440" t="n">
+        <x:v>26.65</x:v>
+      </x:c>
       <x:c r="H72" s="208"/>
       <x:c r="I72" s="208"/>
-      <x:c r="J72" s="208"/>
-      <x:c r="K72" s="208"/>
-      <x:c r="L72" s="208"/>
+      <x:c r="J72" s="308" t="str">
+        <x:v>Tasa estadística estimada</x:v>
+      </x:c>
+      <x:c r="K72" s="308" t="str">
+        <x:v>% CIF</x:v>
+      </x:c>
+      <x:c r="L72" s="443" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
       <x:c r="M72" s="208"/>
       <x:c r="N72" s="208"/>
       <x:c r="O72" s="226"/>
@@ -5290,14 +6219,26 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D73" s="208"/>
-      <x:c r="E73" s="208"/>
-      <x:c r="F73" s="208"/>
-      <x:c r="G73" s="208"/>
+      <x:c r="E73" s="308" t="str">
+        <x:v>Pulsera: armado e inspección</x:v>
+      </x:c>
+      <x:c r="F73" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G73" s="441" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="H73" s="208"/>
       <x:c r="I73" s="208"/>
-      <x:c r="J73" s="208"/>
-      <x:c r="K73" s="208"/>
-      <x:c r="L73" s="208"/>
+      <x:c r="J73" s="308" t="str">
+        <x:v>IVA estimado</x:v>
+      </x:c>
+      <x:c r="K73" s="308" t="str">
+        <x:v>% CIF</x:v>
+      </x:c>
+      <x:c r="L73" s="443" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
       <x:c r="M73" s="208"/>
       <x:c r="N73" s="208"/>
       <x:c r="O73" s="226"/>
@@ -5316,14 +6257,27 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D74" s="208"/>
-      <x:c r="E74" s="208"/>
-      <x:c r="F74" s="208"/>
-      <x:c r="G74" s="208"/>
+      <x:c r="E74" s="308" t="str">
+        <x:v>Pulsera: programación</x:v>
+      </x:c>
+      <x:c r="F74" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G74" s="441" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="H74" s="208"/>
       <x:c r="I74" s="208"/>
-      <x:c r="J74" s="208"/>
-      <x:c r="K74" s="208"/>
-      <x:c r="L74" s="208"/>
+      <x:c r="J74" s="308" t="str">
+        <x:v>Carga presupuestaria simplificada</x:v>
+      </x:c>
+      <x:c r="K74" s="308" t="str">
+        <x:v>45% CIF</x:v>
+      </x:c>
+      <x:c r="L74" s="313" t="n">
+        <x:f>L70*45%</x:f>
+        <x:v>45.0585</x:v>
+      </x:c>
       <x:c r="M74" s="208"/>
       <x:c r="N74" s="208"/>
       <x:c r="O74" s="226"/>
@@ -5342,14 +6296,26 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D75" s="208"/>
-      <x:c r="E75" s="208"/>
-      <x:c r="F75" s="208"/>
-      <x:c r="G75" s="208"/>
+      <x:c r="E75" s="308" t="str">
+        <x:v>Pulsera: prueba funcional</x:v>
+      </x:c>
+      <x:c r="F75" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G75" s="441" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="H75" s="208"/>
       <x:c r="I75" s="208"/>
-      <x:c r="J75" s="208"/>
-      <x:c r="K75" s="208"/>
-      <x:c r="L75" s="208"/>
+      <x:c r="J75" s="308" t="str">
+        <x:v>Gestión de importación y despacho</x:v>
+      </x:c>
+      <x:c r="K75" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L75" s="440" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="M75" s="208"/>
       <x:c r="N75" s="208"/>
       <x:c r="O75" s="226"/>
@@ -5368,14 +6334,26 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="D76" s="208"/>
-      <x:c r="E76" s="208"/>
-      <x:c r="F76" s="208"/>
-      <x:c r="G76" s="208"/>
+      <x:c r="E76" s="308" t="str">
+        <x:v>Pulsera: registro y trazabilidad</x:v>
+      </x:c>
+      <x:c r="F76" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G76" s="441" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="H76" s="208"/>
       <x:c r="I76" s="208"/>
-      <x:c r="J76" s="208"/>
-      <x:c r="K76" s="208"/>
-      <x:c r="L76" s="208"/>
+      <x:c r="J76" s="308" t="str">
+        <x:v>Traslado local</x:v>
+      </x:c>
+      <x:c r="K76" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L76" s="440" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="M76" s="208"/>
       <x:c r="N76" s="208"/>
       <x:c r="O76" s="226"/>
@@ -5394,14 +6372,27 @@
         <x:v>1.4</x:v>
       </x:c>
       <x:c r="D77" s="208"/>
-      <x:c r="E77" s="208"/>
-      <x:c r="F77" s="208"/>
-      <x:c r="G77" s="208"/>
+      <x:c r="E77" s="308" t="str">
+        <x:v>Pulsera: total</x:v>
+      </x:c>
+      <x:c r="F77" s="308" t="str">
+        <x:v>min/u</x:v>
+      </x:c>
+      <x:c r="G77" s="316" t="n">
+        <x:f>SUM(G73:G76)</x:f>
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="H77" s="208"/>
       <x:c r="I77" s="208"/>
-      <x:c r="J77" s="208"/>
-      <x:c r="K77" s="208"/>
-      <x:c r="L77" s="208"/>
+      <x:c r="J77" s="308" t="str">
+        <x:v>Recepción e inventario</x:v>
+      </x:c>
+      <x:c r="K77" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L77" s="440" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="M77" s="208"/>
       <x:c r="N77" s="208"/>
       <x:c r="O77" s="226"/>
@@ -5420,14 +6411,28 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="D78" s="208"/>
-      <x:c r="E78" s="208"/>
-      <x:c r="F78" s="208"/>
-      <x:c r="G78" s="208"/>
+      <x:c r="E78" s="308" t="str">
+        <x:v>Pulsera: mano de obra</x:v>
+      </x:c>
+      <x:c r="F78" s="308" t="str">
+        <x:v>USD/u</x:v>
+      </x:c>
+      <x:c r="G78" s="313" t="n">
+        <x:f>ROUND(G77/60*$C$80,2)</x:f>
+        <x:v>5.1</x:v>
+      </x:c>
       <x:c r="H78" s="208"/>
       <x:c r="I78" s="208"/>
-      <x:c r="J78" s="208"/>
-      <x:c r="K78" s="208"/>
-      <x:c r="L78" s="208"/>
+      <x:c r="J78" s="317" t="str">
+        <x:v>Logística e importación por kit</x:v>
+      </x:c>
+      <x:c r="K78" s="317" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L78" s="318" t="n">
+        <x:f>SUM(L68:L69,L74:L77)</x:f>
+        <x:v>69.05850000000001</x:v>
+      </x:c>
       <x:c r="M78" s="208"/>
       <x:c r="N78" s="208"/>
       <x:c r="O78" s="226"/>
@@ -5447,14 +6452,27 @@
         <x:v>20.416666666666664</x:v>
       </x:c>
       <x:c r="D79" s="208"/>
-      <x:c r="E79" s="208"/>
-      <x:c r="F79" s="208"/>
-      <x:c r="G79" s="208"/>
+      <x:c r="E79" s="308" t="str">
+        <x:v>Parche: materiales</x:v>
+      </x:c>
+      <x:c r="F79" s="308" t="str">
+        <x:v>USD/u</x:v>
+      </x:c>
+      <x:c r="G79" s="440" t="n">
+        <x:v>7.25</x:v>
+      </x:c>
       <x:c r="H79" s="208"/>
       <x:c r="I79" s="208"/>
-      <x:c r="J79" s="208"/>
-      <x:c r="K79" s="208"/>
-      <x:c r="L79" s="208"/>
+      <x:c r="J79" s="317" t="str">
+        <x:v>Almacenamiento inicial</x:v>
+      </x:c>
+      <x:c r="K79" s="317" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L79" s="318" t="n">
+        <x:f>$C$68/$C$65</x:f>
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="M79" s="208"/>
       <x:c r="N79" s="208"/>
       <x:c r="O79" s="226"/>
@@ -5474,14 +6492,27 @@
         <x:v>14.583333333333334</x:v>
       </x:c>
       <x:c r="D80" s="208"/>
-      <x:c r="E80" s="208"/>
-      <x:c r="F80" s="208"/>
-      <x:c r="G80" s="208"/>
+      <x:c r="E80" s="308" t="str">
+        <x:v>Parche: horas por 100 unidades</x:v>
+      </x:c>
+      <x:c r="F80" s="308" t="str">
+        <x:v>h/100 u</x:v>
+      </x:c>
+      <x:c r="G80" s="440" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="H80" s="208"/>
       <x:c r="I80" s="208"/>
-      <x:c r="J80" s="208"/>
-      <x:c r="K80" s="208"/>
-      <x:c r="L80" s="208"/>
+      <x:c r="J80" s="319" t="str">
+        <x:v>Presupuesto por kit en Argentina</x:v>
+      </x:c>
+      <x:c r="K80" s="319" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L80" s="320" t="n">
+        <x:f>SUM($C$66:$C$67,L79)</x:f>
+        <x:v>174.51850000000002</x:v>
+      </x:c>
       <x:c r="M80" s="208"/>
       <x:c r="N80" s="208"/>
       <x:c r="O80" s="226"/>
@@ -5500,9 +6531,16 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="D81" s="208"/>
-      <x:c r="E81" s="208"/>
-      <x:c r="F81" s="208"/>
-      <x:c r="G81" s="208"/>
+      <x:c r="E81" s="308" t="str">
+        <x:v>Parche: tarifa productiva</x:v>
+      </x:c>
+      <x:c r="F81" s="308" t="str">
+        <x:v>USD/h</x:v>
+      </x:c>
+      <x:c r="G81" s="313" t="n">
+        <x:f>$C$79</x:f>
+        <x:v>20.416666666666664</x:v>
+      </x:c>
       <x:c r="H81" s="208"/>
       <x:c r="I81" s="208"/>
       <x:c r="J81" s="208"/>
@@ -5526,14 +6564,23 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="D82" s="208"/>
-      <x:c r="E82" s="208"/>
-      <x:c r="F82" s="208"/>
-      <x:c r="G82" s="208"/>
+      <x:c r="E82" s="308" t="str">
+        <x:v>Parche: mano de obra</x:v>
+      </x:c>
+      <x:c r="F82" s="308" t="str">
+        <x:v>USD/u</x:v>
+      </x:c>
+      <x:c r="G82" s="313" t="n">
+        <x:f>ROUND(G80/100*G81,2)</x:f>
+        <x:v>4.08</x:v>
+      </x:c>
       <x:c r="H82" s="208"/>
       <x:c r="I82" s="208"/>
-      <x:c r="J82" s="208"/>
-      <x:c r="K82" s="208"/>
-      <x:c r="L82" s="208"/>
+      <x:c r="J82" s="435" t="str">
+        <x:v>Preserie año 1 sin doble mano de obra</x:v>
+      </x:c>
+      <x:c r="K82" s="436"/>
+      <x:c r="L82" s="437"/>
       <x:c r="M82" s="208"/>
       <x:c r="N82" s="208"/>
       <x:c r="O82" s="226"/>
@@ -5552,14 +6599,27 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="D83" s="208"/>
-      <x:c r="E83" s="208"/>
-      <x:c r="F83" s="208"/>
-      <x:c r="G83" s="208"/>
+      <x:c r="E83" s="308" t="str">
+        <x:v>Empaque y accesorios</x:v>
+      </x:c>
+      <x:c r="F83" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="G83" s="440" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="H83" s="208"/>
       <x:c r="I83" s="208"/>
-      <x:c r="J83" s="208"/>
-      <x:c r="K83" s="208"/>
-      <x:c r="L83" s="208"/>
+      <x:c r="J83" s="317" t="str">
+        <x:v>Costo directo preserie sin MO interna</x:v>
+      </x:c>
+      <x:c r="K83" s="317" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L83" s="318" t="n">
+        <x:f>SUM(G65,G72,G79,G83:G84)</x:f>
+        <x:v>87.19999999999999</x:v>
+      </x:c>
       <x:c r="M83" s="208"/>
       <x:c r="N83" s="208"/>
       <x:c r="O83" s="226"/>
@@ -5578,14 +6638,27 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="D84" s="208"/>
-      <x:c r="E84" s="208"/>
-      <x:c r="F84" s="208"/>
-      <x:c r="G84" s="208"/>
+      <x:c r="E84" s="308" t="str">
+        <x:v>Cargo fijo de proveedor sin cotización</x:v>
+      </x:c>
+      <x:c r="F84" s="308" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="G84" s="440" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="H84" s="208"/>
       <x:c r="I84" s="208"/>
-      <x:c r="J84" s="208"/>
-      <x:c r="K84" s="208"/>
-      <x:c r="L84" s="208"/>
+      <x:c r="J84" s="317" t="str">
+        <x:v>Valor importado preserie</x:v>
+      </x:c>
+      <x:c r="K84" s="317" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L84" s="318" t="n">
+        <x:f>SUM(G65,G72)</x:f>
+        <x:v>75.94999999999999</x:v>
+      </x:c>
       <x:c r="M84" s="208"/>
       <x:c r="N84" s="208"/>
       <x:c r="O84" s="226"/>
@@ -5604,14 +6677,28 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="D85" s="208"/>
-      <x:c r="E85" s="208"/>
-      <x:c r="F85" s="208"/>
-      <x:c r="G85" s="208"/>
+      <x:c r="E85" s="317" t="str">
+        <x:v>Costo directo de fabricación por kit</x:v>
+      </x:c>
+      <x:c r="F85" s="317" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="G85" s="318" t="n">
+        <x:f>SUM(G65,G71,G72,G78,G79,G82:G84)</x:f>
+        <x:v>102.46</x:v>
+      </x:c>
       <x:c r="H85" s="208"/>
       <x:c r="I85" s="208"/>
-      <x:c r="J85" s="208"/>
-      <x:c r="K85" s="208"/>
-      <x:c r="L85" s="208"/>
+      <x:c r="J85" s="317" t="str">
+        <x:v>CIF preserie</x:v>
+      </x:c>
+      <x:c r="K85" s="317" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L85" s="318" t="n">
+        <x:f>SUM(L84,L68:L69)</x:f>
+        <x:v>88.94999999999999</x:v>
+      </x:c>
       <x:c r="M85" s="208"/>
       <x:c r="N85" s="208"/>
       <x:c r="O85" s="226"/>
@@ -5630,14 +6717,28 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="D86" s="208"/>
-      <x:c r="E86" s="208"/>
-      <x:c r="F86" s="208"/>
-      <x:c r="G86" s="208"/>
+      <x:c r="E86" s="319" t="str">
+        <x:v>Costo directo por parche</x:v>
+      </x:c>
+      <x:c r="F86" s="319" t="str">
+        <x:v>USD/u</x:v>
+      </x:c>
+      <x:c r="G86" s="320" t="n">
+        <x:f>SUM(G79,G82)</x:f>
+        <x:v>11.33</x:v>
+      </x:c>
       <x:c r="H86" s="208"/>
       <x:c r="I86" s="208"/>
-      <x:c r="J86" s="208"/>
-      <x:c r="K86" s="208"/>
-      <x:c r="L86" s="208"/>
+      <x:c r="J86" s="319" t="str">
+        <x:v>Logística/importación preserie</x:v>
+      </x:c>
+      <x:c r="K86" s="319" t="str">
+        <x:v>USD/kit</x:v>
+      </x:c>
+      <x:c r="L86" s="320" t="n">
+        <x:f>SUM(L68:L69,L85*45%,L75:L77)</x:f>
+        <x:v>64.0275</x:v>
+      </x:c>
       <x:c r="M86" s="208"/>
       <x:c r="N86" s="208"/>
       <x:c r="O86" s="226"/>
@@ -5673,31 +6774,34 @@
     </x:row>
     <x:row r="88" ht="21" customHeight="1">
       <x:c r="A88" s="196" t="str">
-        <x:v>Consultas médicas, legales y regulatorias</x:v>
+        <x:v>Consultas especializadas (sin bioquímica)</x:v>
       </x:c>
       <x:c r="B88" s="196" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="C88" s="230" t="n">
+      <x:c r="C88" s="298" t="n">
+        <x:f>P69</x:f>
         <x:v>10000</x:v>
       </x:c>
       <x:c r="D88" s="208"/>
-      <x:c r="E88" s="208"/>
-      <x:c r="F88" s="208"/>
-      <x:c r="G88" s="208"/>
-      <x:c r="H88" s="208"/>
-      <x:c r="I88" s="208"/>
-      <x:c r="J88" s="208"/>
-      <x:c r="K88" s="208"/>
-      <x:c r="L88" s="208"/>
-      <x:c r="M88" s="208"/>
-      <x:c r="N88" s="208"/>
-      <x:c r="O88" s="226"/>
-      <x:c r="P88" s="226"/>
+      <x:c r="E88" s="435" t="str">
+        <x:v>Criterios de costeo e importación</x:v>
+      </x:c>
+      <x:c r="F88" s="436"/>
+      <x:c r="G88" s="436"/>
+      <x:c r="H88" s="436"/>
+      <x:c r="I88" s="436"/>
+      <x:c r="J88" s="436"/>
+      <x:c r="K88" s="436"/>
+      <x:c r="L88" s="436"/>
+      <x:c r="M88" s="436"/>
+      <x:c r="N88" s="436"/>
+      <x:c r="O88" s="436"/>
+      <x:c r="P88" s="437"/>
       <x:c r="Q88" s="226"/>
       <x:c r="R88" s="226"/>
     </x:row>
-    <x:row r="89" ht="21" customHeight="1">
+    <x:row r="89" ht="24" customHeight="1">
       <x:c r="A89" s="196" t="str">
         <x:v>QA y validación técnica externa</x:v>
       </x:c>
@@ -5708,22 +6812,24 @@
         <x:v>8000</x:v>
       </x:c>
       <x:c r="D89" s="208"/>
-      <x:c r="E89" s="208"/>
-      <x:c r="F89" s="208"/>
-      <x:c r="G89" s="208"/>
-      <x:c r="H89" s="208"/>
-      <x:c r="I89" s="208"/>
-      <x:c r="J89" s="208"/>
-      <x:c r="K89" s="208"/>
-      <x:c r="L89" s="208"/>
-      <x:c r="M89" s="208"/>
-      <x:c r="N89" s="208"/>
-      <x:c r="O89" s="226"/>
-      <x:c r="P89" s="226"/>
+      <x:c r="E89" s="333" t="str">
+        <x:v>Los tiempos y tarifas de armado, programación y prueba son estimaciones internas de producción; no constituyen cotizaciones de proveedor.</x:v>
+      </x:c>
+      <x:c r="F89" s="333"/>
+      <x:c r="G89" s="333"/>
+      <x:c r="H89" s="333"/>
+      <x:c r="I89" s="333"/>
+      <x:c r="J89" s="333"/>
+      <x:c r="K89" s="333"/>
+      <x:c r="L89" s="333"/>
+      <x:c r="M89" s="333"/>
+      <x:c r="N89" s="333"/>
+      <x:c r="O89" s="334"/>
+      <x:c r="P89" s="334"/>
       <x:c r="Q89" s="226"/>
       <x:c r="R89" s="226"/>
     </x:row>
-    <x:row r="90" ht="21" customHeight="1">
+    <x:row r="90" ht="24" customHeight="1">
       <x:c r="A90" s="196" t="str">
         <x:v>Merma de fabricación</x:v>
       </x:c>
@@ -5734,22 +6840,24 @@
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="D90" s="208"/>
-      <x:c r="E90" s="208"/>
-      <x:c r="F90" s="208"/>
-      <x:c r="G90" s="208"/>
-      <x:c r="H90" s="208"/>
-      <x:c r="I90" s="208"/>
-      <x:c r="J90" s="208"/>
-      <x:c r="K90" s="208"/>
-      <x:c r="L90" s="208"/>
-      <x:c r="M90" s="208"/>
-      <x:c r="N90" s="208"/>
-      <x:c r="O90" s="226"/>
-      <x:c r="P90" s="226"/>
+      <x:c r="E90" s="333" t="str">
+        <x:v>En el año 1 el armado final, la programación, la prueba y la preparación del parche quedan cubiertos por los cuatro FTE: la preserie usa un costo específico sin esa mano de obra. En los años 2 a 4 sí forman parte del costo variable unitario.</x:v>
+      </x:c>
+      <x:c r="F90" s="333"/>
+      <x:c r="G90" s="333"/>
+      <x:c r="H90" s="333"/>
+      <x:c r="I90" s="333"/>
+      <x:c r="J90" s="333"/>
+      <x:c r="K90" s="333"/>
+      <x:c r="L90" s="333"/>
+      <x:c r="M90" s="333"/>
+      <x:c r="N90" s="333"/>
+      <x:c r="O90" s="334"/>
+      <x:c r="P90" s="334"/>
       <x:c r="Q90" s="226"/>
       <x:c r="R90" s="226"/>
     </x:row>
-    <x:row r="91" ht="21" customHeight="1">
+    <x:row r="91" ht="24" customHeight="1">
       <x:c r="A91" s="196" t="str">
         <x:v>Costo comercial variable sobre ventas</x:v>
       </x:c>
@@ -5760,22 +6868,24 @@
         <x:v>0.08</x:v>
       </x:c>
       <x:c r="D91" s="208"/>
-      <x:c r="E91" s="208"/>
-      <x:c r="F91" s="208"/>
-      <x:c r="G91" s="208"/>
-      <x:c r="H91" s="208"/>
-      <x:c r="I91" s="208"/>
-      <x:c r="J91" s="208"/>
-      <x:c r="K91" s="208"/>
-      <x:c r="L91" s="208"/>
-      <x:c r="M91" s="208"/>
-      <x:c r="N91" s="208"/>
-      <x:c r="O91" s="226"/>
-      <x:c r="P91" s="226"/>
+      <x:c r="E91" s="333" t="str">
+        <x:v>El cargo fijo de proveedor permanece editable en cero hasta contar con evidencia. La merma se aplica mediante unidades brutas, no mediante un multiplicador general.</x:v>
+      </x:c>
+      <x:c r="F91" s="333"/>
+      <x:c r="G91" s="333"/>
+      <x:c r="H91" s="333"/>
+      <x:c r="I91" s="333"/>
+      <x:c r="J91" s="333"/>
+      <x:c r="K91" s="333"/>
+      <x:c r="L91" s="333"/>
+      <x:c r="M91" s="333"/>
+      <x:c r="N91" s="333"/>
+      <x:c r="O91" s="334"/>
+      <x:c r="P91" s="334"/>
       <x:c r="Q91" s="226"/>
       <x:c r="R91" s="226"/>
     </x:row>
-    <x:row r="92" ht="21" customHeight="1">
+    <x:row r="92" ht="24" customHeight="1">
       <x:c r="A92" s="196" t="str">
         <x:v>Costo mensual por FTE comercial</x:v>
       </x:c>
@@ -5786,22 +6896,24 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="D92" s="208"/>
-      <x:c r="E92" s="208"/>
-      <x:c r="F92" s="208"/>
-      <x:c r="G92" s="208"/>
-      <x:c r="H92" s="208"/>
-      <x:c r="I92" s="208"/>
-      <x:c r="J92" s="208"/>
-      <x:c r="K92" s="208"/>
-      <x:c r="L92" s="208"/>
-      <x:c r="M92" s="208"/>
-      <x:c r="N92" s="208"/>
-      <x:c r="O92" s="226"/>
-      <x:c r="P92" s="226"/>
+      <x:c r="E92" s="333" t="str">
+        <x:v>La carga de importación es una previsión académica simplificada del 45% sobre CIF; una operación real debe verificar la posición arancelaria y el tratamiento fiscal aplicable.</x:v>
+      </x:c>
+      <x:c r="F92" s="333"/>
+      <x:c r="G92" s="333"/>
+      <x:c r="H92" s="333"/>
+      <x:c r="I92" s="333"/>
+      <x:c r="J92" s="333"/>
+      <x:c r="K92" s="333"/>
+      <x:c r="L92" s="333"/>
+      <x:c r="M92" s="333"/>
+      <x:c r="N92" s="333"/>
+      <x:c r="O92" s="334"/>
+      <x:c r="P92" s="334"/>
       <x:c r="Q92" s="226"/>
       <x:c r="R92" s="226"/>
     </x:row>
-    <x:row r="93" ht="21" customHeight="1">
+    <x:row r="93" ht="24" customHeight="1">
       <x:c r="A93" s="196" t="str">
         <x:v>Difusión mensual de referencia</x:v>
       </x:c>
@@ -5812,18 +6924,20 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="D93" s="208"/>
-      <x:c r="E93" s="208"/>
-      <x:c r="F93" s="208"/>
-      <x:c r="G93" s="208"/>
-      <x:c r="H93" s="208"/>
-      <x:c r="I93" s="208"/>
-      <x:c r="J93" s="208"/>
-      <x:c r="K93" s="208"/>
-      <x:c r="L93" s="208"/>
-      <x:c r="M93" s="208"/>
-      <x:c r="N93" s="208"/>
-      <x:c r="O93" s="226"/>
-      <x:c r="P93" s="226"/>
+      <x:c r="E93" s="333" t="str">
+        <x:v>En explotación se presupuestan lector y pulsera ensamblados desde China. Para la preserie del año 1 se importan sus materiales y procesos base; el armado final, la programación, la prueba, el parche y el acondicionamiento se realizan con la dotación interna.</x:v>
+      </x:c>
+      <x:c r="F93" s="333"/>
+      <x:c r="G93" s="333"/>
+      <x:c r="H93" s="333"/>
+      <x:c r="I93" s="333"/>
+      <x:c r="J93" s="333"/>
+      <x:c r="K93" s="333"/>
+      <x:c r="L93" s="333"/>
+      <x:c r="M93" s="333"/>
+      <x:c r="N93" s="333"/>
+      <x:c r="O93" s="334"/>
+      <x:c r="P93" s="334"/>
       <x:c r="Q93" s="226"/>
       <x:c r="R93" s="226"/>
     </x:row>
@@ -6818,16 +7932,16 @@
       <x:c r="N132" s="208"/>
       <x:c r="O132" s="238"/>
       <x:c r="P132" s="238" t="n">
-        <x:f>ROUNDUP(MAX(0,P131-N62)+P131*$C$102,0)</x:f>
-        <x:v>230</x:v>
+        <x:f>ROUNDUP(MAX(0,P131+P135+P131*$C$102-N62),0)</x:f>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="Q132" s="238" t="n">
-        <x:f>ROUNDUP(MAX(0,Q131-P62)+Q131*$C$102,0)</x:f>
-        <x:v>850</x:v>
+        <x:f>ROUNDUP(MAX(0,Q131+Q135+Q131*$C$102-P62),0)</x:f>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="R132" s="238" t="n">
-        <x:f>ROUNDUP(MAX(0,R131-Q62)+R131*$C$102,0)</x:f>
-        <x:v>1768</x:v>
+        <x:f>ROUNDUP(MAX(0,R131+R135+R131*$C$102-Q62),0)</x:f>
+        <x:v>1792</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="21" customHeight="1">
@@ -6893,7 +8007,9 @@
       </x:c>
     </x:row>
     <x:row r="135" ht="21" customHeight="1">
-      <x:c r="A135" s="196"/>
+      <x:c r="A135" s="196" t="str">
+        <x:v>Kits demostradores a clínicas</x:v>
+      </x:c>
       <x:c r="B135" s="196"/>
       <x:c r="C135" s="208"/>
       <x:c r="D135" s="208"/>
@@ -6908,9 +8024,18 @@
       <x:c r="M135" s="208"/>
       <x:c r="N135" s="208"/>
       <x:c r="O135" s="226"/>
-      <x:c r="P135" s="226"/>
-      <x:c r="Q135" s="226"/>
-      <x:c r="R135" s="226"/>
+      <x:c r="P135" s="226" t="n">
+        <x:f>'Plan comercial'!C62</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q135" s="226" t="n">
+        <x:f>'Plan comercial'!D62</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="R135" s="226" t="n">
+        <x:f>'Plan comercial'!E62</x:f>
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="136" ht="21" customHeight="1">
       <x:c r="A136" s="198" t="str">
@@ -7157,15 +8282,15 @@
       <x:c r="O144" s="241"/>
       <x:c r="P144" s="241" t="n">
         <x:f t="shared" ref="P144:R144" si="78">P45</x:f>
-        <x:v>-27425.39930241555</x:v>
+        <x:v>15968.373475362197</x:v>
       </x:c>
       <x:c r="Q144" s="241" t="n">
         <x:f t="shared" si="78">Q45</x:f>
-        <x:v>-34512.47278186551</x:v>
+        <x:v>139335.2688848012</x:v>
       </x:c>
       <x:c r="R144" s="241" t="n">
         <x:f t="shared" si="78">R45</x:f>
-        <x:v>43149.620072317775</x:v>
+        <x:v>451017.52896120655</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="21" customHeight="1">
@@ -7212,7 +8337,7 @@
     </x:row>
     <x:row r="147" ht="21" customHeight="1">
       <x:c r="A147" s="205" t="str">
-        <x:v>La producción repone el inventario consumido, cubre el objetivo de cierre e incorpora la merma antes de valorizar costos.</x:v>
+        <x:v>La producción repone inventario, cubre demostradores, alcanza el objetivo de cierre e incorpora la merma antes de valorizar costos.</x:v>
       </x:c>
       <x:c r="B147" s="196"/>
       <x:c r="C147" s="208"/>
@@ -7899,7 +9024,7 @@
       </x:c>
       <x:c r="G175" s="246" t="n">
         <x:f>K45</x:f>
-        <x:v>-25656.666666666664</x:v>
+        <x:v>-22044.444444444445</x:v>
       </x:c>
       <x:c r="H175" s="208"/>
       <x:c r="I175" s="208"/>
@@ -7927,7 +9052,7 @@
       </x:c>
       <x:c r="G176" s="246" t="n">
         <x:f>L45</x:f>
-        <x:v>-33498</x:v>
+        <x:v>-27812.944444444445</x:v>
       </x:c>
       <x:c r="H176" s="208"/>
       <x:c r="I176" s="208"/>
@@ -7955,7 +9080,7 @@
       </x:c>
       <x:c r="G177" s="246" t="n">
         <x:f>M45</x:f>
-        <x:v>-18227.555555555555</x:v>
+        <x:v>-16845.666666666668</x:v>
       </x:c>
       <x:c r="H177" s="208"/>
       <x:c r="I177" s="208"/>
@@ -8011,7 +9136,7 @@
       </x:c>
       <x:c r="G179" s="246" t="n">
         <x:f>P45</x:f>
-        <x:v>-27425.39930241555</x:v>
+        <x:v>15968.373475362197</x:v>
       </x:c>
       <x:c r="H179" s="208"/>
       <x:c r="I179" s="208"/>
@@ -8039,7 +9164,7 @@
       </x:c>
       <x:c r="G180" s="246" t="n">
         <x:f>Q45</x:f>
-        <x:v>-34512.47278186551</x:v>
+        <x:v>139335.2688848012</x:v>
       </x:c>
       <x:c r="H180" s="208"/>
       <x:c r="I180" s="208"/>
@@ -8067,7 +9192,7 @@
       </x:c>
       <x:c r="G181" s="246" t="n">
         <x:f>R45</x:f>
-        <x:v>43149.620072317775</x:v>
+        <x:v>451017.52896120655</x:v>
       </x:c>
       <x:c r="H181" s="208"/>
       <x:c r="I181" s="208"/>
@@ -11501,6 +12626,13 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="E89:P89"/>
+    <x:mergeCell ref="E90:P90"/>
+    <x:mergeCell ref="E91:P91"/>
+    <x:mergeCell ref="E92:P92"/>
+    <x:mergeCell ref="E93:P93"/>
+  </x:mergeCells>
   <x:conditionalFormatting sqref="C43:N43">
     <x:cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
       <x:formula>-0.005</x:formula>
@@ -11512,9 +12644,9 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re05b6a7b337a400f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf99cefe441194293"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5aaa2a725407429d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29be34b19bbc45c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13500,9 +14632,1273 @@
       <x:c r="U51" s="271"/>
       <x:c r="V51" s="271"/>
     </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="435" t="str">
+        <x:v>Años 2 a 4: Kanban comercial/operativo y objetivos trimestrales</x:v>
+      </x:c>
+      <x:c r="B54" s="436"/>
+      <x:c r="C54" s="436"/>
+      <x:c r="D54" s="436"/>
+      <x:c r="E54" s="436"/>
+      <x:c r="F54" s="436"/>
+      <x:c r="G54" s="436"/>
+      <x:c r="H54" s="436"/>
+      <x:c r="I54" s="436"/>
+      <x:c r="J54" s="436"/>
+      <x:c r="K54" s="436"/>
+      <x:c r="L54" s="436"/>
+      <x:c r="M54" s="436"/>
+      <x:c r="N54" s="436"/>
+      <x:c r="O54" s="436"/>
+      <x:c r="P54" s="436"/>
+      <x:c r="Q54" s="436"/>
+      <x:c r="R54" s="436"/>
+      <x:c r="S54" s="436"/>
+      <x:c r="T54" s="436"/>
+      <x:c r="U54" s="436"/>
+      <x:c r="V54" s="437"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="369" t="str">
+        <x:v>El tablero se revisa semanalmente; las metas trimestrales se reconcilian con el escenario activo del plan comercial y con el flujo de fondos.</x:v>
+      </x:c>
+      <x:c r="B55" s="369"/>
+      <x:c r="C55" s="369"/>
+      <x:c r="D55" s="369"/>
+      <x:c r="E55" s="369"/>
+      <x:c r="F55" s="369"/>
+      <x:c r="G55" s="369"/>
+      <x:c r="H55" s="369"/>
+      <x:c r="I55" s="369"/>
+      <x:c r="J55" s="369"/>
+      <x:c r="K55" s="369"/>
+      <x:c r="L55" s="369"/>
+      <x:c r="M55" s="369"/>
+      <x:c r="N55" s="369"/>
+      <x:c r="O55" s="369"/>
+      <x:c r="P55" s="369"/>
+      <x:c r="Q55" s="369"/>
+      <x:c r="R55" s="369"/>
+      <x:c r="S55" s="369"/>
+      <x:c r="T55" s="369"/>
+      <x:c r="U55" s="369"/>
+      <x:c r="V55" s="369"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="367"/>
+      <x:c r="B56" s="367"/>
+      <x:c r="C56" s="367"/>
+      <x:c r="D56" s="367"/>
+      <x:c r="E56" s="367"/>
+      <x:c r="F56" s="367"/>
+      <x:c r="G56" s="367"/>
+      <x:c r="H56" s="367"/>
+      <x:c r="I56" s="367"/>
+      <x:c r="J56" s="367"/>
+      <x:c r="K56" s="367"/>
+      <x:c r="L56" s="367"/>
+      <x:c r="M56" s="367"/>
+      <x:c r="N56" s="367"/>
+      <x:c r="O56" s="367"/>
+      <x:c r="P56" s="367"/>
+      <x:c r="Q56" s="367"/>
+      <x:c r="R56" s="367"/>
+      <x:c r="S56" s="367"/>
+      <x:c r="T56" s="367"/>
+      <x:c r="U56" s="367"/>
+      <x:c r="V56" s="367"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="435" t="str">
+        <x:v>Columnas del tablero Kanban</x:v>
+      </x:c>
+      <x:c r="B57" s="436"/>
+      <x:c r="C57" s="436"/>
+      <x:c r="D57" s="436"/>
+      <x:c r="E57" s="436"/>
+      <x:c r="F57" s="436"/>
+      <x:c r="G57" s="436"/>
+      <x:c r="H57" s="437"/>
+      <x:c r="I57" s="367"/>
+      <x:c r="J57" s="367"/>
+      <x:c r="K57" s="367"/>
+      <x:c r="L57" s="367"/>
+      <x:c r="M57" s="367"/>
+      <x:c r="N57" s="367"/>
+      <x:c r="O57" s="367"/>
+      <x:c r="P57" s="367"/>
+      <x:c r="Q57" s="367"/>
+      <x:c r="R57" s="367"/>
+      <x:c r="S57" s="367"/>
+      <x:c r="T57" s="367"/>
+      <x:c r="U57" s="367"/>
+      <x:c r="V57" s="367"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="454" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="B58" s="454" t="str">
+        <x:v>Prospectado</x:v>
+      </x:c>
+      <x:c r="C58" s="454" t="str">
+        <x:v>Contactado</x:v>
+      </x:c>
+      <x:c r="D58" s="454" t="str">
+        <x:v>Reunión</x:v>
+      </x:c>
+      <x:c r="E58" s="454" t="str">
+        <x:v>Acuerdo</x:v>
+      </x:c>
+      <x:c r="F58" s="454" t="str">
+        <x:v>Onboarding</x:v>
+      </x:c>
+      <x:c r="G58" s="454" t="str">
+        <x:v>Aliado activo</x:v>
+      </x:c>
+      <x:c r="H58" s="454" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="I58" s="367"/>
+      <x:c r="J58" s="367"/>
+      <x:c r="K58" s="367"/>
+      <x:c r="L58" s="367"/>
+      <x:c r="M58" s="367"/>
+      <x:c r="N58" s="367"/>
+      <x:c r="O58" s="367"/>
+      <x:c r="P58" s="367"/>
+      <x:c r="Q58" s="367"/>
+      <x:c r="R58" s="367"/>
+      <x:c r="S58" s="367"/>
+      <x:c r="T58" s="367"/>
+      <x:c r="U58" s="367"/>
+      <x:c r="V58" s="367"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="369" t="str">
+        <x:v>Cada tarjeta conserva responsable, próxima acción, fecha objetivo, evidencia y desvío; ningún acuerdo avanza a activo sin onboarding registrado.</x:v>
+      </x:c>
+      <x:c r="B59" s="369"/>
+      <x:c r="C59" s="369"/>
+      <x:c r="D59" s="369"/>
+      <x:c r="E59" s="369"/>
+      <x:c r="F59" s="369"/>
+      <x:c r="G59" s="369"/>
+      <x:c r="H59" s="369"/>
+      <x:c r="I59" s="367"/>
+      <x:c r="J59" s="367"/>
+      <x:c r="K59" s="367"/>
+      <x:c r="L59" s="367"/>
+      <x:c r="M59" s="367"/>
+      <x:c r="N59" s="367"/>
+      <x:c r="O59" s="367"/>
+      <x:c r="P59" s="367"/>
+      <x:c r="Q59" s="367"/>
+      <x:c r="R59" s="367"/>
+      <x:c r="S59" s="367"/>
+      <x:c r="T59" s="367"/>
+      <x:c r="U59" s="367"/>
+      <x:c r="V59" s="367"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="367"/>
+      <x:c r="B60" s="367"/>
+      <x:c r="C60" s="367"/>
+      <x:c r="D60" s="367"/>
+      <x:c r="E60" s="367"/>
+      <x:c r="F60" s="367"/>
+      <x:c r="G60" s="367"/>
+      <x:c r="H60" s="367"/>
+      <x:c r="I60" s="367"/>
+      <x:c r="J60" s="367"/>
+      <x:c r="K60" s="367"/>
+      <x:c r="L60" s="367"/>
+      <x:c r="M60" s="367"/>
+      <x:c r="N60" s="367"/>
+      <x:c r="O60" s="367"/>
+      <x:c r="P60" s="367"/>
+      <x:c r="Q60" s="367"/>
+      <x:c r="R60" s="367"/>
+      <x:c r="S60" s="367"/>
+      <x:c r="T60" s="367"/>
+      <x:c r="U60" s="367"/>
+      <x:c r="V60" s="367"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="435" t="str">
+        <x:v>Frentes paralelos</x:v>
+      </x:c>
+      <x:c r="B61" s="436"/>
+      <x:c r="C61" s="436"/>
+      <x:c r="D61" s="436"/>
+      <x:c r="E61" s="437"/>
+      <x:c r="F61" s="367"/>
+      <x:c r="G61" s="367"/>
+      <x:c r="H61" s="367"/>
+      <x:c r="I61" s="367"/>
+      <x:c r="J61" s="367"/>
+      <x:c r="K61" s="367"/>
+      <x:c r="L61" s="367"/>
+      <x:c r="M61" s="367"/>
+      <x:c r="N61" s="367"/>
+      <x:c r="O61" s="367"/>
+      <x:c r="P61" s="367"/>
+      <x:c r="Q61" s="367"/>
+      <x:c r="R61" s="367"/>
+      <x:c r="S61" s="367"/>
+      <x:c r="T61" s="367"/>
+      <x:c r="U61" s="367"/>
+      <x:c r="V61" s="367"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="454" t="str">
+        <x:v>Frente</x:v>
+      </x:c>
+      <x:c r="B62" s="454" t="str">
+        <x:v>Objetivo</x:v>
+      </x:c>
+      <x:c r="C62" s="454" t="str">
+        <x:v>Indicador</x:v>
+      </x:c>
+      <x:c r="D62" s="454" t="str">
+        <x:v>Cadencia</x:v>
+      </x:c>
+      <x:c r="E62" s="454" t="str">
+        <x:v>Responsable</x:v>
+      </x:c>
+      <x:c r="F62" s="367"/>
+      <x:c r="G62" s="367"/>
+      <x:c r="H62" s="367"/>
+      <x:c r="I62" s="367"/>
+      <x:c r="J62" s="367"/>
+      <x:c r="K62" s="367"/>
+      <x:c r="L62" s="367"/>
+      <x:c r="M62" s="367"/>
+      <x:c r="N62" s="367"/>
+      <x:c r="O62" s="367"/>
+      <x:c r="P62" s="367"/>
+      <x:c r="Q62" s="367"/>
+      <x:c r="R62" s="367"/>
+      <x:c r="S62" s="367"/>
+      <x:c r="T62" s="367"/>
+      <x:c r="U62" s="367"/>
+      <x:c r="V62" s="367"/>
+    </x:row>
+    <x:row r="63" ht="30" customHeight="1">
+      <x:c r="A63" s="360" t="str">
+        <x:v>Médicos</x:v>
+      </x:c>
+      <x:c r="B63" s="360" t="str">
+        <x:v>Activar el canal principal</x:v>
+      </x:c>
+      <x:c r="C63" s="360" t="str">
+        <x:v>Prospectos, conversión, aliados y pacientes</x:v>
+      </x:c>
+      <x:c r="D63" s="360" t="str">
+        <x:v>Semanal</x:v>
+      </x:c>
+      <x:c r="E63" s="360" t="str">
+        <x:v>Comercial</x:v>
+      </x:c>
+      <x:c r="F63" s="367"/>
+      <x:c r="G63" s="367"/>
+      <x:c r="H63" s="367"/>
+      <x:c r="I63" s="367"/>
+      <x:c r="J63" s="367"/>
+      <x:c r="K63" s="367"/>
+      <x:c r="L63" s="367"/>
+      <x:c r="M63" s="367"/>
+      <x:c r="N63" s="367"/>
+      <x:c r="O63" s="367"/>
+      <x:c r="P63" s="367"/>
+      <x:c r="Q63" s="367"/>
+      <x:c r="R63" s="367"/>
+      <x:c r="S63" s="367"/>
+      <x:c r="T63" s="367"/>
+      <x:c r="U63" s="367"/>
+      <x:c r="V63" s="367"/>
+    </x:row>
+    <x:row r="64" ht="30" customHeight="1">
+      <x:c r="A64" s="360" t="str">
+        <x:v>Clínicas</x:v>
+      </x:c>
+      <x:c r="B64" s="360" t="str">
+        <x:v>Demostraciones y acuerdos institucionales</x:v>
+      </x:c>
+      <x:c r="C64" s="360" t="str">
+        <x:v>Reuniones, acuerdos, demos y onboarding</x:v>
+      </x:c>
+      <x:c r="D64" s="360" t="str">
+        <x:v>Semanal</x:v>
+      </x:c>
+      <x:c r="E64" s="360" t="str">
+        <x:v>Comercial + legal</x:v>
+      </x:c>
+      <x:c r="F64" s="367"/>
+      <x:c r="G64" s="367"/>
+      <x:c r="H64" s="367"/>
+      <x:c r="I64" s="367"/>
+      <x:c r="J64" s="367"/>
+      <x:c r="K64" s="367"/>
+      <x:c r="L64" s="367"/>
+      <x:c r="M64" s="367"/>
+      <x:c r="N64" s="367"/>
+      <x:c r="O64" s="367"/>
+      <x:c r="P64" s="367"/>
+      <x:c r="Q64" s="367"/>
+      <x:c r="R64" s="367"/>
+      <x:c r="S64" s="367"/>
+      <x:c r="T64" s="367"/>
+      <x:c r="U64" s="367"/>
+      <x:c r="V64" s="367"/>
+    </x:row>
+    <x:row r="65" ht="30" customHeight="1">
+      <x:c r="A65" s="360" t="str">
+        <x:v>Proveedores y producción</x:v>
+      </x:c>
+      <x:c r="B65" s="360" t="str">
+        <x:v>Cumplir volumen, costo y calidad</x:v>
+      </x:c>
+      <x:c r="C65" s="360" t="str">
+        <x:v>Unidades, costo, merma y aceptación</x:v>
+      </x:c>
+      <x:c r="D65" s="360" t="str">
+        <x:v>Quincenal</x:v>
+      </x:c>
+      <x:c r="E65" s="360" t="str">
+        <x:v>Operaciones + QA</x:v>
+      </x:c>
+      <x:c r="F65" s="367"/>
+      <x:c r="G65" s="367"/>
+      <x:c r="H65" s="367"/>
+      <x:c r="I65" s="367"/>
+      <x:c r="J65" s="367"/>
+      <x:c r="K65" s="367"/>
+      <x:c r="L65" s="367"/>
+      <x:c r="M65" s="367"/>
+      <x:c r="N65" s="367"/>
+      <x:c r="O65" s="367"/>
+      <x:c r="P65" s="367"/>
+      <x:c r="Q65" s="367"/>
+      <x:c r="R65" s="367"/>
+      <x:c r="S65" s="367"/>
+      <x:c r="T65" s="367"/>
+      <x:c r="U65" s="367"/>
+      <x:c r="V65" s="367"/>
+    </x:row>
+    <x:row r="66" ht="30" customHeight="1">
+      <x:c r="A66" s="360" t="str">
+        <x:v>Inventario y logística</x:v>
+      </x:c>
+      <x:c r="B66" s="360" t="str">
+        <x:v>Evitar quiebres y excedentes</x:v>
+      </x:c>
+      <x:c r="C66" s="360" t="str">
+        <x:v>Stock, cobertura, tránsito y recepciones</x:v>
+      </x:c>
+      <x:c r="D66" s="360" t="str">
+        <x:v>Semanal</x:v>
+      </x:c>
+      <x:c r="E66" s="360" t="str">
+        <x:v>Operaciones</x:v>
+      </x:c>
+      <x:c r="F66" s="367"/>
+      <x:c r="G66" s="367"/>
+      <x:c r="H66" s="367"/>
+      <x:c r="I66" s="367"/>
+      <x:c r="J66" s="367"/>
+      <x:c r="K66" s="367"/>
+      <x:c r="L66" s="367"/>
+      <x:c r="M66" s="367"/>
+      <x:c r="N66" s="367"/>
+      <x:c r="O66" s="367"/>
+      <x:c r="P66" s="367"/>
+      <x:c r="Q66" s="367"/>
+      <x:c r="R66" s="367"/>
+      <x:c r="S66" s="367"/>
+      <x:c r="T66" s="367"/>
+      <x:c r="U66" s="367"/>
+      <x:c r="V66" s="367"/>
+    </x:row>
+    <x:row r="67" ht="30" customHeight="1">
+      <x:c r="A67" s="360" t="str">
+        <x:v>Soporte y QA de campo</x:v>
+      </x:c>
+      <x:c r="B67" s="360" t="str">
+        <x:v>Resolver incidentes y capturar evidencia</x:v>
+      </x:c>
+      <x:c r="C67" s="360" t="str">
+        <x:v>Horas, tickets, fallas y cierre</x:v>
+      </x:c>
+      <x:c r="D67" s="360" t="str">
+        <x:v>Quincenal</x:v>
+      </x:c>
+      <x:c r="E67" s="360" t="str">
+        <x:v>Soporte + QA</x:v>
+      </x:c>
+      <x:c r="F67" s="367"/>
+      <x:c r="G67" s="367"/>
+      <x:c r="H67" s="367"/>
+      <x:c r="I67" s="367"/>
+      <x:c r="J67" s="367"/>
+      <x:c r="K67" s="367"/>
+      <x:c r="L67" s="367"/>
+      <x:c r="M67" s="367"/>
+      <x:c r="N67" s="367"/>
+      <x:c r="O67" s="367"/>
+      <x:c r="P67" s="367"/>
+      <x:c r="Q67" s="367"/>
+      <x:c r="R67" s="367"/>
+      <x:c r="S67" s="367"/>
+      <x:c r="T67" s="367"/>
+      <x:c r="U67" s="367"/>
+      <x:c r="V67" s="367"/>
+    </x:row>
+    <x:row r="68" ht="30" customHeight="1">
+      <x:c r="A68" s="360" t="str">
+        <x:v>Mejoras del producto</x:v>
+      </x:c>
+      <x:c r="B68" s="360" t="str">
+        <x:v>Priorizar evidencia y uso real</x:v>
+      </x:c>
+      <x:c r="C68" s="360" t="str">
+        <x:v>Historias cerradas y defectos</x:v>
+      </x:c>
+      <x:c r="D68" s="360" t="str">
+        <x:v>Sprint</x:v>
+      </x:c>
+      <x:c r="E68" s="360" t="str">
+        <x:v>Producto + ingeniería</x:v>
+      </x:c>
+      <x:c r="F68" s="367"/>
+      <x:c r="G68" s="367"/>
+      <x:c r="H68" s="367"/>
+      <x:c r="I68" s="367"/>
+      <x:c r="J68" s="367"/>
+      <x:c r="K68" s="367"/>
+      <x:c r="L68" s="367"/>
+      <x:c r="M68" s="367"/>
+      <x:c r="N68" s="367"/>
+      <x:c r="O68" s="367"/>
+      <x:c r="P68" s="367"/>
+      <x:c r="Q68" s="367"/>
+      <x:c r="R68" s="367"/>
+      <x:c r="S68" s="367"/>
+      <x:c r="T68" s="367"/>
+      <x:c r="U68" s="367"/>
+      <x:c r="V68" s="367"/>
+    </x:row>
+    <x:row r="69" ht="30" customHeight="1">
+      <x:c r="A69" s="361" t="str">
+        <x:v>Revisión regulatoria</x:v>
+      </x:c>
+      <x:c r="B69" s="361" t="str">
+        <x:v>Mantener límites y requisitos vigentes</x:v>
+      </x:c>
+      <x:c r="C69" s="361" t="str">
+        <x:v>Decisiones, consultas y acciones</x:v>
+      </x:c>
+      <x:c r="D69" s="361" t="str">
+        <x:v>Trimestral</x:v>
+      </x:c>
+      <x:c r="E69" s="361" t="str">
+        <x:v>Regulatorio + legal</x:v>
+      </x:c>
+      <x:c r="F69" s="367"/>
+      <x:c r="G69" s="367"/>
+      <x:c r="H69" s="367"/>
+      <x:c r="I69" s="367"/>
+      <x:c r="J69" s="367"/>
+      <x:c r="K69" s="367"/>
+      <x:c r="L69" s="367"/>
+      <x:c r="M69" s="367"/>
+      <x:c r="N69" s="367"/>
+      <x:c r="O69" s="367"/>
+      <x:c r="P69" s="367"/>
+      <x:c r="Q69" s="367"/>
+      <x:c r="R69" s="367"/>
+      <x:c r="S69" s="367"/>
+      <x:c r="T69" s="367"/>
+      <x:c r="U69" s="367"/>
+      <x:c r="V69" s="367"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="367"/>
+      <x:c r="B70" s="367"/>
+      <x:c r="C70" s="367"/>
+      <x:c r="D70" s="367"/>
+      <x:c r="E70" s="367"/>
+      <x:c r="F70" s="367"/>
+      <x:c r="G70" s="367"/>
+      <x:c r="H70" s="367"/>
+      <x:c r="I70" s="367"/>
+      <x:c r="J70" s="367"/>
+      <x:c r="K70" s="367"/>
+      <x:c r="L70" s="367"/>
+      <x:c r="M70" s="367"/>
+      <x:c r="N70" s="367"/>
+      <x:c r="O70" s="367"/>
+      <x:c r="P70" s="367"/>
+      <x:c r="Q70" s="367"/>
+      <x:c r="R70" s="367"/>
+      <x:c r="S70" s="367"/>
+      <x:c r="T70" s="367"/>
+      <x:c r="U70" s="367"/>
+      <x:c r="V70" s="367"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="435" t="str">
+        <x:v>Metas trimestrales vinculadas al escenario activo</x:v>
+      </x:c>
+      <x:c r="B71" s="436"/>
+      <x:c r="C71" s="436"/>
+      <x:c r="D71" s="436"/>
+      <x:c r="E71" s="436"/>
+      <x:c r="F71" s="436"/>
+      <x:c r="G71" s="436"/>
+      <x:c r="H71" s="436"/>
+      <x:c r="I71" s="437"/>
+      <x:c r="J71" s="367"/>
+      <x:c r="K71" s="367"/>
+      <x:c r="L71" s="367"/>
+      <x:c r="M71" s="367"/>
+      <x:c r="N71" s="367"/>
+      <x:c r="O71" s="367"/>
+      <x:c r="P71" s="367"/>
+      <x:c r="Q71" s="367"/>
+      <x:c r="R71" s="367"/>
+      <x:c r="S71" s="367"/>
+      <x:c r="T71" s="367"/>
+      <x:c r="U71" s="367"/>
+      <x:c r="V71" s="367"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="454" t="str">
+        <x:v>Año</x:v>
+      </x:c>
+      <x:c r="B72" s="454" t="str">
+        <x:v>Trimestre</x:v>
+      </x:c>
+      <x:c r="C72" s="454" t="str">
+        <x:v>Aliados acumulados</x:v>
+      </x:c>
+      <x:c r="D72" s="454" t="str">
+        <x:v>Ventas de kits</x:v>
+      </x:c>
+      <x:c r="E72" s="454" t="str">
+        <x:v>Producción bruta</x:v>
+      </x:c>
+      <x:c r="F72" s="454" t="str">
+        <x:v>Demostradores</x:v>
+      </x:c>
+      <x:c r="G72" s="454" t="str">
+        <x:v>Retención</x:v>
+      </x:c>
+      <x:c r="H72" s="454" t="str">
+        <x:v>Soporte (h)</x:v>
+      </x:c>
+      <x:c r="I72" s="454" t="str">
+        <x:v>Criterio de cierre</x:v>
+      </x:c>
+      <x:c r="J72" s="367"/>
+      <x:c r="K72" s="367"/>
+      <x:c r="L72" s="367"/>
+      <x:c r="M72" s="367"/>
+      <x:c r="N72" s="367"/>
+      <x:c r="O72" s="367"/>
+      <x:c r="P72" s="367"/>
+      <x:c r="Q72" s="367"/>
+      <x:c r="R72" s="367"/>
+      <x:c r="S72" s="367"/>
+      <x:c r="T72" s="367"/>
+      <x:c r="U72" s="367"/>
+      <x:c r="V72" s="367"/>
+    </x:row>
+    <x:row r="73" ht="28" customHeight="1">
+      <x:c r="A73" s="360" t="str">
+        <x:v>Año 2</x:v>
+      </x:c>
+      <x:c r="B73" s="360" t="str">
+        <x:v>T1</x:v>
+      </x:c>
+      <x:c r="C73" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$7*1/4,0)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D73" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$24/4,0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E73" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$P$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F73" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$62/4,0)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G73" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H73" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$P$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I73" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J73" s="367"/>
+      <x:c r="K73" s="367"/>
+      <x:c r="L73" s="367"/>
+      <x:c r="M73" s="367"/>
+      <x:c r="N73" s="367"/>
+      <x:c r="O73" s="367"/>
+      <x:c r="P73" s="367"/>
+      <x:c r="Q73" s="367"/>
+      <x:c r="R73" s="367"/>
+      <x:c r="S73" s="367"/>
+      <x:c r="T73" s="367"/>
+      <x:c r="U73" s="367"/>
+      <x:c r="V73" s="367"/>
+    </x:row>
+    <x:row r="74" ht="28" customHeight="1">
+      <x:c r="A74" s="360" t="str">
+        <x:v>Año 2</x:v>
+      </x:c>
+      <x:c r="B74" s="360" t="str">
+        <x:v>T2</x:v>
+      </x:c>
+      <x:c r="C74" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$7*2/4,0)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D74" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$24/4,0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E74" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$P$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F74" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$62/4,0)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G74" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H74" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$P$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I74" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J74" s="367"/>
+      <x:c r="K74" s="367"/>
+      <x:c r="L74" s="367"/>
+      <x:c r="M74" s="367"/>
+      <x:c r="N74" s="367"/>
+      <x:c r="O74" s="367"/>
+      <x:c r="P74" s="367"/>
+      <x:c r="Q74" s="367"/>
+      <x:c r="R74" s="367"/>
+      <x:c r="S74" s="367"/>
+      <x:c r="T74" s="367"/>
+      <x:c r="U74" s="367"/>
+      <x:c r="V74" s="367"/>
+    </x:row>
+    <x:row r="75" ht="28" customHeight="1">
+      <x:c r="A75" s="360" t="str">
+        <x:v>Año 2</x:v>
+      </x:c>
+      <x:c r="B75" s="360" t="str">
+        <x:v>T3</x:v>
+      </x:c>
+      <x:c r="C75" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$7*3/4,0)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D75" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$24/4,0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E75" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$P$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F75" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$62/4,0)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G75" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H75" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$P$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I75" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J75" s="367"/>
+      <x:c r="K75" s="367"/>
+      <x:c r="L75" s="367"/>
+      <x:c r="M75" s="367"/>
+      <x:c r="N75" s="367"/>
+      <x:c r="O75" s="367"/>
+      <x:c r="P75" s="367"/>
+      <x:c r="Q75" s="367"/>
+      <x:c r="R75" s="367"/>
+      <x:c r="S75" s="367"/>
+      <x:c r="T75" s="367"/>
+      <x:c r="U75" s="367"/>
+      <x:c r="V75" s="367"/>
+    </x:row>
+    <x:row r="76" ht="28" customHeight="1">
+      <x:c r="A76" s="360" t="str">
+        <x:v>Año 2</x:v>
+      </x:c>
+      <x:c r="B76" s="360" t="str">
+        <x:v>T4</x:v>
+      </x:c>
+      <x:c r="C76" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!C$7*4/4,0)</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D76" s="360" t="n">
+        <x:f>'Plan comercial'!C$24-SUM(D73:D75)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E76" s="360" t="n">
+        <x:f>ROUNDUP('Flujo de caja'!$P$132/(1-'Flujo de caja'!$C$90),0)-SUM(E73:E75)</x:f>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F76" s="360" t="n">
+        <x:f>'Plan comercial'!C$62-SUM(F73:F75)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G76" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H76" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$P$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="I76" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J76" s="367"/>
+      <x:c r="K76" s="367"/>
+      <x:c r="L76" s="367"/>
+      <x:c r="M76" s="367"/>
+      <x:c r="N76" s="367"/>
+      <x:c r="O76" s="367"/>
+      <x:c r="P76" s="367"/>
+      <x:c r="Q76" s="367"/>
+      <x:c r="R76" s="367"/>
+      <x:c r="S76" s="367"/>
+      <x:c r="T76" s="367"/>
+      <x:c r="U76" s="367"/>
+      <x:c r="V76" s="367"/>
+    </x:row>
+    <x:row r="77" ht="28" customHeight="1">
+      <x:c r="A77" s="360" t="str">
+        <x:v>Año 3</x:v>
+      </x:c>
+      <x:c r="B77" s="360" t="str">
+        <x:v>T1</x:v>
+      </x:c>
+      <x:c r="C77" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$7*1/4,0)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D77" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$24/4,0)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E77" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$Q$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F77" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$62/4,0)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G77" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H77" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$Q$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="I77" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J77" s="367"/>
+      <x:c r="K77" s="367"/>
+      <x:c r="L77" s="367"/>
+      <x:c r="M77" s="367"/>
+      <x:c r="N77" s="367"/>
+      <x:c r="O77" s="367"/>
+      <x:c r="P77" s="367"/>
+      <x:c r="Q77" s="367"/>
+      <x:c r="R77" s="367"/>
+      <x:c r="S77" s="367"/>
+      <x:c r="T77" s="367"/>
+      <x:c r="U77" s="367"/>
+      <x:c r="V77" s="367"/>
+    </x:row>
+    <x:row r="78" ht="28" customHeight="1">
+      <x:c r="A78" s="360" t="str">
+        <x:v>Año 3</x:v>
+      </x:c>
+      <x:c r="B78" s="360" t="str">
+        <x:v>T2</x:v>
+      </x:c>
+      <x:c r="C78" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$7*2/4,0)</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D78" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$24/4,0)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E78" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$Q$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F78" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$62/4,0)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G78" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H78" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$Q$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="I78" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J78" s="367"/>
+      <x:c r="K78" s="367"/>
+      <x:c r="L78" s="367"/>
+      <x:c r="M78" s="367"/>
+      <x:c r="N78" s="367"/>
+      <x:c r="O78" s="367"/>
+      <x:c r="P78" s="367"/>
+      <x:c r="Q78" s="367"/>
+      <x:c r="R78" s="367"/>
+      <x:c r="S78" s="367"/>
+      <x:c r="T78" s="367"/>
+      <x:c r="U78" s="367"/>
+      <x:c r="V78" s="367"/>
+    </x:row>
+    <x:row r="79" ht="28" customHeight="1">
+      <x:c r="A79" s="360" t="str">
+        <x:v>Año 3</x:v>
+      </x:c>
+      <x:c r="B79" s="360" t="str">
+        <x:v>T3</x:v>
+      </x:c>
+      <x:c r="C79" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$7*3/4,0)</x:f>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D79" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$24/4,0)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E79" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$Q$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F79" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$62/4,0)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G79" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H79" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$Q$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="I79" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J79" s="367"/>
+      <x:c r="K79" s="367"/>
+      <x:c r="L79" s="367"/>
+      <x:c r="M79" s="367"/>
+      <x:c r="N79" s="367"/>
+      <x:c r="O79" s="367"/>
+      <x:c r="P79" s="367"/>
+      <x:c r="Q79" s="367"/>
+      <x:c r="R79" s="367"/>
+      <x:c r="S79" s="367"/>
+      <x:c r="T79" s="367"/>
+      <x:c r="U79" s="367"/>
+      <x:c r="V79" s="367"/>
+    </x:row>
+    <x:row r="80" ht="28" customHeight="1">
+      <x:c r="A80" s="360" t="str">
+        <x:v>Año 3</x:v>
+      </x:c>
+      <x:c r="B80" s="360" t="str">
+        <x:v>T4</x:v>
+      </x:c>
+      <x:c r="C80" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!D$7*4/4,0)</x:f>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D80" s="360" t="n">
+        <x:f>'Plan comercial'!D$24-SUM(D77:D79)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E80" s="360" t="n">
+        <x:f>ROUNDUP('Flujo de caja'!$Q$132/(1-'Flujo de caja'!$C$90),0)-SUM(E77:E79)</x:f>
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="F80" s="360" t="n">
+        <x:f>'Plan comercial'!D$62-SUM(F77:F79)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G80" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H80" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$Q$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="I80" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J80" s="367"/>
+      <x:c r="K80" s="367"/>
+      <x:c r="L80" s="367"/>
+      <x:c r="M80" s="367"/>
+      <x:c r="N80" s="367"/>
+      <x:c r="O80" s="367"/>
+      <x:c r="P80" s="367"/>
+      <x:c r="Q80" s="367"/>
+      <x:c r="R80" s="367"/>
+      <x:c r="S80" s="367"/>
+      <x:c r="T80" s="367"/>
+      <x:c r="U80" s="367"/>
+      <x:c r="V80" s="367"/>
+    </x:row>
+    <x:row r="81" ht="28" customHeight="1">
+      <x:c r="A81" s="360" t="str">
+        <x:v>Año 4</x:v>
+      </x:c>
+      <x:c r="B81" s="360" t="str">
+        <x:v>T1</x:v>
+      </x:c>
+      <x:c r="C81" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$7*1/4,0)</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D81" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$24/4,0)</x:f>
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="E81" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$R$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="F81" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$62/4,0)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G81" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H81" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$R$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>1558</x:v>
+      </x:c>
+      <x:c r="I81" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J81" s="367"/>
+      <x:c r="K81" s="367"/>
+      <x:c r="L81" s="367"/>
+      <x:c r="M81" s="367"/>
+      <x:c r="N81" s="367"/>
+      <x:c r="O81" s="367"/>
+      <x:c r="P81" s="367"/>
+      <x:c r="Q81" s="367"/>
+      <x:c r="R81" s="367"/>
+      <x:c r="S81" s="367"/>
+      <x:c r="T81" s="367"/>
+      <x:c r="U81" s="367"/>
+      <x:c r="V81" s="367"/>
+    </x:row>
+    <x:row r="82" ht="28" customHeight="1">
+      <x:c r="A82" s="360" t="str">
+        <x:v>Año 4</x:v>
+      </x:c>
+      <x:c r="B82" s="360" t="str">
+        <x:v>T2</x:v>
+      </x:c>
+      <x:c r="C82" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$7*2/4,0)</x:f>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D82" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$24/4,0)</x:f>
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="E82" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$R$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="F82" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$62/4,0)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G82" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H82" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$R$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>1558</x:v>
+      </x:c>
+      <x:c r="I82" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J82" s="367"/>
+      <x:c r="K82" s="367"/>
+      <x:c r="L82" s="367"/>
+      <x:c r="M82" s="367"/>
+      <x:c r="N82" s="367"/>
+      <x:c r="O82" s="367"/>
+      <x:c r="P82" s="367"/>
+      <x:c r="Q82" s="367"/>
+      <x:c r="R82" s="367"/>
+      <x:c r="S82" s="367"/>
+      <x:c r="T82" s="367"/>
+      <x:c r="U82" s="367"/>
+      <x:c r="V82" s="367"/>
+    </x:row>
+    <x:row r="83" ht="28" customHeight="1">
+      <x:c r="A83" s="360" t="str">
+        <x:v>Año 4</x:v>
+      </x:c>
+      <x:c r="B83" s="360" t="str">
+        <x:v>T3</x:v>
+      </x:c>
+      <x:c r="C83" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$7*3/4,0)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D83" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$24/4,0)</x:f>
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="E83" s="360" t="n">
+        <x:f>ROUNDUP(('Flujo de caja'!$R$132/(1-'Flujo de caja'!$C$90))/4,0)</x:f>
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="F83" s="360" t="n">
+        <x:f>ROUND('Plan comercial'!E$62/4,0)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G83" s="365" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H83" s="360" t="n">
+        <x:f>ROUND('Flujo de caja'!$R$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>1558</x:v>
+      </x:c>
+      <x:c r="I83" s="360" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J83" s="367"/>
+      <x:c r="K83" s="367"/>
+      <x:c r="L83" s="367"/>
+      <x:c r="M83" s="367"/>
+      <x:c r="N83" s="367"/>
+      <x:c r="O83" s="367"/>
+      <x:c r="P83" s="367"/>
+      <x:c r="Q83" s="367"/>
+      <x:c r="R83" s="367"/>
+      <x:c r="S83" s="367"/>
+      <x:c r="T83" s="367"/>
+      <x:c r="U83" s="367"/>
+      <x:c r="V83" s="367"/>
+    </x:row>
+    <x:row r="84" ht="28" customHeight="1">
+      <x:c r="A84" s="361" t="str">
+        <x:v>Año 4</x:v>
+      </x:c>
+      <x:c r="B84" s="361" t="str">
+        <x:v>T4</x:v>
+      </x:c>
+      <x:c r="C84" s="361" t="n">
+        <x:f>ROUND('Plan comercial'!E$7*4/4,0)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D84" s="361" t="n">
+        <x:f>'Plan comercial'!E$24-SUM(D81:D83)</x:f>
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="E84" s="361" t="n">
+        <x:f>ROUNDUP('Flujo de caja'!$R$132/(1-'Flujo de caja'!$C$90),0)-SUM(E81:E83)</x:f>
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="F84" s="361" t="n">
+        <x:f>'Plan comercial'!E$62-SUM(F81:F83)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G84" s="366" t="n">
+        <x:f>'Flujo de caja'!$C$101</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="H84" s="361" t="n">
+        <x:f>ROUND('Flujo de caja'!$R$60*'Flujo de caja'!$C$94/100*3,0)</x:f>
+        <x:v>1558</x:v>
+      </x:c>
+      <x:c r="I84" s="361" t="str">
+        <x:v>Metas revisadas; 100% de desvíos críticos con responsable y fecha</x:v>
+      </x:c>
+      <x:c r="J84" s="367"/>
+      <x:c r="K84" s="367"/>
+      <x:c r="L84" s="367"/>
+      <x:c r="M84" s="367"/>
+      <x:c r="N84" s="367"/>
+      <x:c r="O84" s="367"/>
+      <x:c r="P84" s="367"/>
+      <x:c r="Q84" s="367"/>
+      <x:c r="R84" s="367"/>
+      <x:c r="S84" s="367"/>
+      <x:c r="T84" s="367"/>
+      <x:c r="U84" s="367"/>
+      <x:c r="V84" s="367"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="367"/>
+      <x:c r="B85" s="367"/>
+      <x:c r="C85" s="367"/>
+      <x:c r="D85" s="367"/>
+      <x:c r="E85" s="367"/>
+      <x:c r="F85" s="367"/>
+      <x:c r="G85" s="367"/>
+      <x:c r="H85" s="367"/>
+      <x:c r="I85" s="367"/>
+      <x:c r="J85" s="367"/>
+      <x:c r="K85" s="367"/>
+      <x:c r="L85" s="367"/>
+      <x:c r="M85" s="367"/>
+      <x:c r="N85" s="367"/>
+      <x:c r="O85" s="367"/>
+      <x:c r="P85" s="367"/>
+      <x:c r="Q85" s="367"/>
+      <x:c r="R85" s="367"/>
+      <x:c r="S85" s="367"/>
+      <x:c r="T85" s="367"/>
+      <x:c r="U85" s="367"/>
+      <x:c r="V85" s="367"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="369" t="str">
+        <x:v>La producción bruta incluye la merma y concilia con el volumen anual del flujo; los demostradores y el onboarding comienzan únicamente en el año 2.</x:v>
+      </x:c>
+      <x:c r="B86" s="369"/>
+      <x:c r="C86" s="369"/>
+      <x:c r="D86" s="369"/>
+      <x:c r="E86" s="369"/>
+      <x:c r="F86" s="369"/>
+      <x:c r="G86" s="369"/>
+      <x:c r="H86" s="369"/>
+      <x:c r="I86" s="369"/>
+      <x:c r="J86" s="367"/>
+      <x:c r="K86" s="367"/>
+      <x:c r="L86" s="367"/>
+      <x:c r="M86" s="367"/>
+      <x:c r="N86" s="367"/>
+      <x:c r="O86" s="367"/>
+      <x:c r="P86" s="367"/>
+      <x:c r="Q86" s="367"/>
+      <x:c r="R86" s="367"/>
+      <x:c r="S86" s="367"/>
+      <x:c r="T86" s="367"/>
+      <x:c r="U86" s="367"/>
+      <x:c r="V86" s="367"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A34:I34"/>
+    <x:mergeCell ref="A55:V55"/>
+    <x:mergeCell ref="A59:H59"/>
+    <x:mergeCell ref="A86:I86"/>
+    <x:mergeCell ref="E58:F58"/>
+    <x:mergeCell ref="A59:I59"/>
+    <x:mergeCell ref="B62:C62"/>
+    <x:mergeCell ref="D62:F62"/>
+    <x:mergeCell ref="H62:I62"/>
+    <x:mergeCell ref="B63:C63"/>
+    <x:mergeCell ref="D63:F63"/>
+    <x:mergeCell ref="H63:I63"/>
+    <x:mergeCell ref="B64:C64"/>
+    <x:mergeCell ref="D64:F64"/>
+    <x:mergeCell ref="H64:I64"/>
+    <x:mergeCell ref="B65:C65"/>
+    <x:mergeCell ref="D65:F65"/>
+    <x:mergeCell ref="H65:I65"/>
+    <x:mergeCell ref="B66:C66"/>
+    <x:mergeCell ref="D66:F66"/>
+    <x:mergeCell ref="H66:I66"/>
+    <x:mergeCell ref="B67:C67"/>
+    <x:mergeCell ref="D67:F67"/>
+    <x:mergeCell ref="H67:I67"/>
+    <x:mergeCell ref="B68:C68"/>
+    <x:mergeCell ref="D68:F68"/>
+    <x:mergeCell ref="H68:I68"/>
+    <x:mergeCell ref="B69:C69"/>
+    <x:mergeCell ref="D69:F69"/>
+    <x:mergeCell ref="H69:I69"/>
+    <x:mergeCell ref="E72:F72"/>
+    <x:mergeCell ref="J72:V72"/>
+    <x:mergeCell ref="E73:F73"/>
+    <x:mergeCell ref="J73:V73"/>
+    <x:mergeCell ref="E74:F74"/>
+    <x:mergeCell ref="J74:V74"/>
+    <x:mergeCell ref="E75:F75"/>
+    <x:mergeCell ref="J75:V75"/>
+    <x:mergeCell ref="E76:F76"/>
+    <x:mergeCell ref="J76:V76"/>
+    <x:mergeCell ref="E77:F77"/>
+    <x:mergeCell ref="J77:V77"/>
+    <x:mergeCell ref="E78:F78"/>
+    <x:mergeCell ref="J78:V78"/>
+    <x:mergeCell ref="E79:F79"/>
+    <x:mergeCell ref="J79:V79"/>
+    <x:mergeCell ref="E80:F80"/>
+    <x:mergeCell ref="J80:V80"/>
+    <x:mergeCell ref="E81:F81"/>
+    <x:mergeCell ref="J81:V81"/>
+    <x:mergeCell ref="E82:F82"/>
+    <x:mergeCell ref="J82:V82"/>
+    <x:mergeCell ref="E83:F83"/>
+    <x:mergeCell ref="J83:V83"/>
+    <x:mergeCell ref="E84:F84"/>
+    <x:mergeCell ref="J84:V84"/>
+    <x:mergeCell ref="A86:V86"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -14150,7 +16546,451 @@
       <x:c r="D49" s="91"/>
       <x:c r="E49" s="91"/>
     </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="435" t="str">
+        <x:v>Canales de adquisición y costos de activación</x:v>
+      </x:c>
+      <x:c r="B52" s="436"/>
+      <x:c r="C52" s="436"/>
+      <x:c r="D52" s="436"/>
+      <x:c r="E52" s="437"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="454" t="str">
+        <x:v>Driver</x:v>
+      </x:c>
+      <x:c r="B53" s="454" t="str">
+        <x:v>Tarifa / criterio</x:v>
+      </x:c>
+      <x:c r="C53" s="454" t="str">
+        <x:v>Año 2</x:v>
+      </x:c>
+      <x:c r="D53" s="454" t="str">
+        <x:v>Año 3</x:v>
+      </x:c>
+      <x:c r="E53" s="454" t="str">
+        <x:v>Año 4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="455" t="str">
+        <x:v>Médicos aliados - selección activa</x:v>
+      </x:c>
+      <x:c r="B54" s="455"/>
+      <x:c r="C54" s="455" t="n">
+        <x:f>ROUND(C7*C56/(C56+C57),0)</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D54" s="455" t="n">
+        <x:f>ROUND(D7*D56/(D56+D57),0)</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E54" s="455" t="n">
+        <x:f>ROUND(E7*E56/(E56+E57),0)</x:f>
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="455" t="str">
+        <x:v>Clínicas aliadas - selección activa</x:v>
+      </x:c>
+      <x:c r="B55" s="455"/>
+      <x:c r="C55" s="455" t="n">
+        <x:f>C7-C54</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D55" s="455" t="n">
+        <x:f>D7-D54</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E55" s="455" t="n">
+        <x:f>E7-E54</x:f>
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="349" t="str">
+        <x:v>Médicos aliados - base aprobada</x:v>
+      </x:c>
+      <x:c r="B56" s="349"/>
+      <x:c r="C56" s="459" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D56" s="459" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E56" s="459" t="n">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="349" t="str">
+        <x:v>Clínicas aliadas - base aprobada</x:v>
+      </x:c>
+      <x:c r="B57" s="349"/>
+      <x:c r="C57" s="459" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D57" s="459" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E57" s="459" t="n">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="349" t="str">
+        <x:v>Prospectos médicos calificados</x:v>
+      </x:c>
+      <x:c r="B58" s="349"/>
+      <x:c r="C58" s="349" t="n">
+        <x:f>ROUND(C54/C59,0)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D58" s="349" t="n">
+        <x:f>ROUND(D54/D59,0)</x:f>
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="E58" s="349" t="n">
+        <x:f>ROUND(E54/E59,0)</x:f>
+        <x:v>280</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="349" t="str">
+        <x:v>Conversión de prospectos médicos</x:v>
+      </x:c>
+      <x:c r="B59" s="349"/>
+      <x:c r="C59" s="460" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D59" s="460" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="E59" s="460" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="349" t="str">
+        <x:v>Prospectos de clínicas calificadas</x:v>
+      </x:c>
+      <x:c r="B60" s="349"/>
+      <x:c r="C60" s="349" t="n">
+        <x:f>ROUND(C55/C61,0)</x:f>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D60" s="349" t="n">
+        <x:f>ROUND(D55/D61,0)</x:f>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E60" s="349" t="n">
+        <x:f>ROUND(E55/E61,0)</x:f>
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="349" t="str">
+        <x:v>Conversión de prospectos de clínicas</x:v>
+      </x:c>
+      <x:c r="B61" s="349"/>
+      <x:c r="C61" s="460" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D61" s="460" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="E61" s="460" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="349" t="str">
+        <x:v>Kits demostradores (uno por clínica)</x:v>
+      </x:c>
+      <x:c r="B62" s="349"/>
+      <x:c r="C62" s="349" t="n">
+        <x:f>C55</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D62" s="349" t="n">
+        <x:f>D55</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E62" s="349" t="n">
+        <x:f>E55</x:f>
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="349" t="str">
+        <x:v>Onboarding de médicos (USD)</x:v>
+      </x:c>
+      <x:c r="B63" s="461" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C63" s="358" t="n">
+        <x:f>C54*$B$63</x:f>
+        <x:v>1350</x:v>
+      </x:c>
+      <x:c r="D63" s="358" t="n">
+        <x:f>D54*$B$63</x:f>
+        <x:v>2625</x:v>
+      </x:c>
+      <x:c r="E63" s="358" t="n">
+        <x:f>E54*$B$63</x:f>
+        <x:v>4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="349" t="str">
+        <x:v>Onboarding de clínicas (USD)</x:v>
+      </x:c>
+      <x:c r="B64" s="461" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C64" s="358" t="n">
+        <x:f>C55*$B$64</x:f>
+        <x:v>2100</x:v>
+      </x:c>
+      <x:c r="D64" s="358" t="n">
+        <x:f>D55*$B$64</x:f>
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="E64" s="358" t="n">
+        <x:f>E55*$B$64</x:f>
+        <x:v>7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="457" t="str">
+        <x:v>Onboarding total (USD)</x:v>
+      </x:c>
+      <x:c r="B65" s="462"/>
+      <x:c r="C65" s="462" t="n">
+        <x:f>SUM(C63:C64)</x:f>
+        <x:v>3450</x:v>
+      </x:c>
+      <x:c r="D65" s="462" t="n">
+        <x:f>SUM(D63:D64)</x:f>
+        <x:v>7125</x:v>
+      </x:c>
+      <x:c r="E65" s="462" t="n">
+        <x:f>SUM(E63:E64)</x:f>
+        <x:v>11400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="367"/>
+      <x:c r="B66" s="367"/>
+      <x:c r="C66" s="367"/>
+      <x:c r="D66" s="367"/>
+      <x:c r="E66" s="367"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="435" t="str">
+        <x:v>Acciones del canal</x:v>
+      </x:c>
+      <x:c r="B67" s="436"/>
+      <x:c r="C67" s="436"/>
+      <x:c r="D67" s="436"/>
+      <x:c r="E67" s="437"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="454" t="str">
+        <x:v>Etapa</x:v>
+      </x:c>
+      <x:c r="B68" s="454" t="str">
+        <x:v>Evidencia de cierre</x:v>
+      </x:c>
+      <x:c r="C68" s="454" t="str">
+        <x:v>Médicos</x:v>
+      </x:c>
+      <x:c r="D68" s="454" t="str">
+        <x:v>Clínicas</x:v>
+      </x:c>
+      <x:c r="E68" s="454" t="str">
+        <x:v>Responsable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="32" customHeight="1">
+      <x:c r="A69" s="360" t="str">
+        <x:v>Construcción de base</x:v>
+      </x:c>
+      <x:c r="B69" s="360" t="str">
+        <x:v>Registro calificado con fuente y contacto</x:v>
+      </x:c>
+      <x:c r="C69" s="360" t="str">
+        <x:v>Prioridad principal</x:v>
+      </x:c>
+      <x:c r="D69" s="360" t="str">
+        <x:v>Instituciones objetivo</x:v>
+      </x:c>
+      <x:c r="E69" s="360" t="str">
+        <x:v>Comercial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="32" customHeight="1">
+      <x:c r="A70" s="360" t="str">
+        <x:v>Contacto</x:v>
+      </x:c>
+      <x:c r="B70" s="360" t="str">
+        <x:v>Respuesta o siguiente acción registrada</x:v>
+      </x:c>
+      <x:c r="C70" s="360" t="str">
+        <x:v>Contacto individual</x:v>
+      </x:c>
+      <x:c r="D70" s="360" t="str">
+        <x:v>Contacto institucional</x:v>
+      </x:c>
+      <x:c r="E70" s="360" t="str">
+        <x:v>Comercial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="32" customHeight="1">
+      <x:c r="A71" s="360" t="str">
+        <x:v>Reunión</x:v>
+      </x:c>
+      <x:c r="B71" s="360" t="str">
+        <x:v>Necesidad, alcance y objeciones documentadas</x:v>
+      </x:c>
+      <x:c r="C71" s="360" t="str">
+        <x:v>Entrevista breve</x:v>
+      </x:c>
+      <x:c r="D71" s="360" t="str">
+        <x:v>Reunión con decisores</x:v>
+      </x:c>
+      <x:c r="E71" s="360" t="str">
+        <x:v>Comercial + producto</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="32" customHeight="1">
+      <x:c r="A72" s="360" t="str">
+        <x:v>Presentación</x:v>
+      </x:c>
+      <x:c r="B72" s="360" t="str">
+        <x:v>Demostración y límites de uso comunicados</x:v>
+      </x:c>
+      <x:c r="C72" s="360" t="str">
+        <x:v>Material clínico</x:v>
+      </x:c>
+      <x:c r="D72" s="360" t="str">
+        <x:v>Kit demostrador</x:v>
+      </x:c>
+      <x:c r="E72" s="360" t="str">
+        <x:v>Producto + regulatorio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="32" customHeight="1">
+      <x:c r="A73" s="360" t="str">
+        <x:v>Acuerdo</x:v>
+      </x:c>
+      <x:c r="B73" s="360" t="str">
+        <x:v>Condiciones comerciales y soporte aprobados</x:v>
+      </x:c>
+      <x:c r="C73" s="360" t="str">
+        <x:v>Acuerdo de colaboración</x:v>
+      </x:c>
+      <x:c r="D73" s="360" t="str">
+        <x:v>Acuerdo institucional</x:v>
+      </x:c>
+      <x:c r="E73" s="360" t="str">
+        <x:v>Legal + comercial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="32" customHeight="1">
+      <x:c r="A74" s="360" t="str">
+        <x:v>Capacitación</x:v>
+      </x:c>
+      <x:c r="B74" s="360" t="str">
+        <x:v>Asistencia y guía entregada</x:v>
+      </x:c>
+      <x:c r="C74" s="360" t="str">
+        <x:v>Onboarding USD 75</x:v>
+      </x:c>
+      <x:c r="D74" s="360" t="str">
+        <x:v>Onboarding USD 300</x:v>
+      </x:c>
+      <x:c r="E74" s="360" t="str">
+        <x:v>Soporte</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="32" customHeight="1">
+      <x:c r="A75" s="361" t="str">
+        <x:v>Seguimiento</x:v>
+      </x:c>
+      <x:c r="B75" s="361" t="str">
+        <x:v>Actividad, pacientes, soporte y desvíos revisados</x:v>
+      </x:c>
+      <x:c r="C75" s="361" t="str">
+        <x:v>Cadencia mensual</x:v>
+      </x:c>
+      <x:c r="D75" s="361" t="str">
+        <x:v>Cadencia mensual</x:v>
+      </x:c>
+      <x:c r="E75" s="361" t="str">
+        <x:v>Comercial + QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="367"/>
+      <x:c r="B76" s="367"/>
+      <x:c r="C76" s="367"/>
+      <x:c r="D76" s="367"/>
+      <x:c r="E76" s="367"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="435" t="str">
+        <x:v>Notas del canal</x:v>
+      </x:c>
+      <x:c r="B77" s="436"/>
+      <x:c r="C77" s="436"/>
+      <x:c r="D77" s="436"/>
+      <x:c r="E77" s="437"/>
+    </x:row>
+    <x:row r="78" ht="24" customHeight="1">
+      <x:c r="A78" s="368" t="str">
+        <x:v>En el escenario base, los prospectos son 90/175/280 médicos y 35/75/120 clínicas, ambos con conversión del 20%.</x:v>
+      </x:c>
+      <x:c r="B78" s="368"/>
+      <x:c r="C78" s="368"/>
+      <x:c r="D78" s="368"/>
+      <x:c r="E78" s="368"/>
+    </x:row>
+    <x:row r="79" ht="24" customHeight="1">
+      <x:c r="A79" s="368" t="str">
+        <x:v>Los médicos constituyen el canal principal; las clínicas concentran demostraciones, acuerdos institucionales y onboarding.</x:v>
+      </x:c>
+      <x:c r="B79" s="368"/>
+      <x:c r="C79" s="368"/>
+      <x:c r="D79" s="368"/>
+      <x:c r="E79" s="368"/>
+    </x:row>
+    <x:row r="80" ht="24" customHeight="1">
+      <x:c r="A80" s="368" t="str">
+        <x:v>Los demostradores se entregan desde el año 2 y están vinculados a producción, merma, importación e inventario.</x:v>
+      </x:c>
+      <x:c r="B80" s="368"/>
+      <x:c r="C80" s="368"/>
+      <x:c r="D80" s="368"/>
+      <x:c r="E80" s="368"/>
+    </x:row>
+    <x:row r="81" ht="24" customHeight="1">
+      <x:c r="A81" s="368" t="str">
+        <x:v>No se modelan pagos por decisiones ni derivaciones clínicas. El 8% variable remunera comercialización, soporte institucional y cobranza.</x:v>
+      </x:c>
+      <x:c r="B81" s="368"/>
+      <x:c r="C81" s="368"/>
+      <x:c r="D81" s="368"/>
+      <x:c r="E81" s="368"/>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A78:E78"/>
+    <x:mergeCell ref="A79:E79"/>
+    <x:mergeCell ref="A80:E80"/>
+    <x:mergeCell ref="A81:E81"/>
+  </x:mergeCells>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="B2">
       <x:formula1>"1,2,3"</x:formula1>
@@ -14158,4 +16998,228 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="54" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="466" t="str">
+        <x:v>Cambios realizados — corrección integral</x:v>
+      </x:c>
+      <x:c r="B1" s="466"/>
+      <x:c r="C1" s="466"/>
+      <x:c r="D1" s="466"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="476" t="str">
+        <x:v>Resumen informativo. La hoja Flujo de caja sigue siendo la fuente financiera autoritativa.</x:v>
+      </x:c>
+      <x:c r="B2" s="476"/>
+      <x:c r="C2" s="476"/>
+      <x:c r="D2" s="476"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="367"/>
+      <x:c r="B3" s="367"/>
+      <x:c r="C3" s="367"/>
+      <x:c r="D3" s="367"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="454" t="str">
+        <x:v>Área</x:v>
+      </x:c>
+      <x:c r="B4" s="454" t="str">
+        <x:v>Cambio realizado</x:v>
+      </x:c>
+      <x:c r="C4" s="454" t="str">
+        <x:v>Resultado final</x:v>
+      </x:c>
+      <x:c r="D4" s="454" t="str">
+        <x:v>Evidencia en el libro</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="38" customHeight="1">
+      <x:c r="A5" s="471" t="str">
+        <x:v>Planificación</x:v>
+      </x:c>
+      <x:c r="B5" s="360" t="str">
+        <x:v>Se reemplazó el desarrollo corto por dotación anual full-time y metodología híbrida.</x:v>
+      </x:c>
+      <x:c r="C5" s="360" t="str">
+        <x:v>4 FTE · 12 meses · 26 sprints · 7.680 h</x:v>
+      </x:c>
+      <x:c r="D5" s="360" t="str">
+        <x:v>Plan 12 meses</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="38" customHeight="1">
+      <x:c r="A6" s="471" t="str">
+        <x:v>Alcance</x:v>
+      </x:c>
+      <x:c r="B6" s="360" t="str">
+        <x:v>Se separaron prototipo intermedio, candidato a MVP y MVP aceptado.</x:v>
+      </x:c>
+      <x:c r="C6" s="360" t="str">
+        <x:v>Mes 7 · mes 10 · mes 12</x:v>
+      </x:c>
+      <x:c r="D6" s="360" t="str">
+        <x:v>Plan 12 meses</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="38" customHeight="1">
+      <x:c r="A7" s="471" t="str">
+        <x:v>FODA y riesgos</x:v>
+      </x:c>
+      <x:c r="B7" s="360" t="str">
+        <x:v>Las fortalezas ahora son capacidades internas; integración/calibración se gestiona como riesgo.</x:v>
+      </x:c>
+      <x:c r="C7" s="360" t="str">
+        <x:v>Rúbrica verificable y seguimiento por hitos</x:v>
+      </x:c>
+      <x:c r="D7" s="360" t="str">
+        <x:v>Informe LaTeX</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="38" customHeight="1">
+      <x:c r="A8" s="471" t="str">
+        <x:v>Costeo</x:v>
+      </x:c>
+      <x:c r="B8" s="360" t="str">
+        <x:v>Se eliminó el recargo general y se trazaron armado, programación, prueba y registro.</x:v>
+      </x:c>
+      <x:c r="C8" s="360" t="str">
+        <x:v>Lector USD 6,08 · pulsera USD 5,10 · parche USD 4,08</x:v>
+      </x:c>
+      <x:c r="D8" s="360" t="str">
+        <x:v>Flujo de caja · filas 64–86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="38" customHeight="1">
+      <x:c r="A9" s="471" t="str">
+        <x:v>Preserie año 1</x:v>
+      </x:c>
+      <x:c r="B9" s="360" t="str">
+        <x:v>Se excluyó la mano de obra ya cubierta por los cuatro FTE.</x:v>
+      </x:c>
+      <x:c r="C9" s="360" t="str">
+        <x:v>Directo USD 87,20 · import./logística USD 64,03 · total USD 17.103,06</x:v>
+      </x:c>
+      <x:c r="D9" s="360" t="str">
+        <x:v>Flujo de caja · filas 82–86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="38" customHeight="1">
+      <x:c r="A10" s="471" t="str">
+        <x:v>Importación</x:v>
+      </x:c>
+      <x:c r="B10" s="360" t="str">
+        <x:v>Se reemplazó la provisión fija por una carga académica sobre CIF y partidas separadas.</x:v>
+      </x:c>
+      <x:c r="C10" s="360" t="str">
+        <x:v>45% del CIF · posición arancelaria a verificar</x:v>
+      </x:c>
+      <x:c r="D10" s="360" t="str">
+        <x:v>Flujo de caja · filas 64–80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="38" customHeight="1">
+      <x:c r="A11" s="471" t="str">
+        <x:v>Modelo comercial</x:v>
+      </x:c>
+      <x:c r="B11" s="360" t="str">
+        <x:v>Las ventas se vincularon a aliados, pacientes alcanzables y adopción.</x:v>
+      </x:c>
+      <x:c r="C11" s="360" t="str">
+        <x:v>300 / 800 / 1.680 kits</x:v>
+      </x:c>
+      <x:c r="D11" s="360" t="str">
+        <x:v>Plan comercial</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="38" customHeight="1">
+      <x:c r="A12" s="471" t="str">
+        <x:v>Canales</x:v>
+      </x:c>
+      <x:c r="B12" s="360" t="str">
+        <x:v>Se priorizaron médicos y se reservaron clínicas para demos y acuerdos institucionales.</x:v>
+      </x:c>
+      <x:c r="C12" s="360" t="str">
+        <x:v>Médicos 18/35/56 · clínicas 7/15/24</x:v>
+      </x:c>
+      <x:c r="D12" s="360" t="str">
+        <x:v>Plan comercial · filas 52–81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="38" customHeight="1">
+      <x:c r="A13" s="471" t="str">
+        <x:v>Año 1</x:v>
+      </x:c>
+      <x:c r="B13" s="360" t="str">
+        <x:v>Se mantuvo como etapa de desarrollo e inversión sin ventas ni demostradores.</x:v>
+      </x:c>
+      <x:c r="C13" s="360" t="str">
+        <x:v>Presupuesto y capital mínimo USD 228.303,06</x:v>
+      </x:c>
+      <x:c r="D13" s="360" t="str">
+        <x:v>Flujo de caja</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="38" customHeight="1">
+      <x:c r="A14" s="471" t="str">
+        <x:v>Viabilidad</x:v>
+      </x:c>
+      <x:c r="B14" s="360" t="str">
+        <x:v>Se recalcularon resultados sin aumentar artificialmente las ventas.</x:v>
+      </x:c>
+      <x:c r="C14" s="360" t="str">
+        <x:v>VAN USD 103.250,74 · TIR 36,83%</x:v>
+      </x:c>
+      <x:c r="D14" s="360" t="str">
+        <x:v>Flujo de caja · indicadores</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="38" customHeight="1">
+      <x:c r="A15" s="473" t="str">
+        <x:v>Verificación</x:v>
+      </x:c>
+      <x:c r="B15" s="474" t="str">
+        <x:v>Se probaron escenarios y sensibilidades y se restauró el caso base.</x:v>
+      </x:c>
+      <x:c r="C15" s="474" t="str">
+        <x:v>0 errores de fórmula</x:v>
+      </x:c>
+      <x:c r="D15" s="474" t="str">
+        <x:v>Escaneo del libro y matriz de trazabilidad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="367"/>
+      <x:c r="B16" s="367"/>
+      <x:c r="C16" s="367"/>
+      <x:c r="D16" s="367"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="477" t="str">
+        <x:v>Última conciliación: 22/10/2026 · Excel e informe usan las mismas cifras base.</x:v>
+      </x:c>
+      <x:c r="B17" s="477"/>
+      <x:c r="C17" s="477"/>
+      <x:c r="D17" s="477"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A17:D17"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/Gestion de proyectos practica/outputs/correccion-docente-2026-10-22/Flujo-de-caja-agrupado-VAN-TIR-corregido.xlsx
+++ b/Gestion de proyectos practica/outputs/correccion-docente-2026-10-22/Flujo-de-caja-agrupado-VAN-TIR-corregido.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo de caja" sheetId="1" r:id="Rf8645ace330c4ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan 12 meses" sheetId="2" r:id="R3aaea0becafd43b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan comercial" sheetId="3" r:id="R5193ad010c0f4b46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cambios realizados" sheetId="4" r:id="R133b364554d14496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujo de caja" sheetId="1" r:id="R37b2445fa10b4c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan 12 meses" sheetId="2" r:id="R5395024c6b304e8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan comercial" sheetId="3" r:id="Rc7a26ae95a5048fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cambios realizados" sheetId="4" r:id="R5397a7533a314e64"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Z_97E5A6E8_1452_495C_ADA9_7DBD435A0EEF_.wvu.FilterData" localSheetId="0" hidden="1">'Flujo de caja'!$A$2:$R$43</x:definedName>
@@ -39,7 +39,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="17">
+  <x:numFmts count="19">
     <x:numFmt numFmtId="164" formatCode="[$$]#,##0.00"/>
     <x:numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
     <x:numFmt numFmtId="166" formatCode="[&gt;=0.005]#,##0.00;[&lt;=-0.005](#,##0.00);&quot;-&quot;"/>
@@ -57,6 +57,8 @@
     <x:numFmt numFmtId="206" formatCode="0.00"/>
     <x:numFmt numFmtId="207" formatCode="0"/>
     <x:numFmt numFmtId="208" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
+    <x:numFmt numFmtId="209" formatCode="dd/mm/yyyy"/>
+    <x:numFmt numFmtId="210" formatCode="0.00%"/>
   </x:numFmts>
   <x:fonts count="35">
     <x:font>
@@ -276,7 +278,7 @@
       <x:scheme val="minor"/>
     </x:font>
   </x:fonts>
-  <x:fills count="30">
+  <x:fills count="48">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -391,6 +393,96 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -599,7 +691,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="478">
+  <x:cellXfs count="624">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
@@ -1923,6 +2015,444 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="8" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="8" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="26" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="26" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="8" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="8" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="26" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="8" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="26" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="8" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="30" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="30" fillId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="27" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="31" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="34" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="8" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="8" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="26" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="26" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="8" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="8" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="26" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="8" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="26" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="8" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="30" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="30" fillId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="27" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="40" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="8" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="8" fillId="42" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="26" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="26" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="8" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="8" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="26" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="8" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="26" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="8" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="44" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="45" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="46" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="46" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="168" fontId="30" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="30" fillId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="27" fillId="46" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="47" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="43" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="46" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="46" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -5237,9 +5767,9 @@
         <x:v>TIR anual</x:v>
       </x:c>
       <x:c r="F50" s="221"/>
-      <x:c r="G50" s="221" t="n">
-        <x:f>IF(C51&lt;0,"No determinada",XIRR(G166:G181,F166:F181))</x:f>
-        <x:v>0.36829809694647936</x:v>
+      <x:c r="G50" s="527" t="n">
+        <x:f>XIRR(G166:G181,F166:F181,20%)</x:f>
+        <x:v>0.36829809694647947</x:v>
       </x:c>
       <x:c r="H50" s="220"/>
       <x:c r="I50" s="220"/>
@@ -5765,73 +6295,73 @@
       </x:c>
     </x:row>
     <x:row r="63" ht="21" customHeight="1">
-      <x:c r="A63" s="446" t="str">
+      <x:c r="A63" s="594" t="str">
         <x:v>Kits demostradores entregados a clínicas</x:v>
       </x:c>
-      <x:c r="B63" s="446" t="str">
+      <x:c r="B63" s="594" t="str">
         <x:v>unidades</x:v>
       </x:c>
-      <x:c r="C63" s="447" t="n">
+      <x:c r="C63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D63" s="447" t="n">
+      <x:c r="D63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E63" s="447" t="n">
+      <x:c r="E63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F63" s="447" t="n">
+      <x:c r="F63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G63" s="447" t="n">
+      <x:c r="G63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H63" s="447" t="n">
+      <x:c r="H63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I63" s="447" t="n">
+      <x:c r="I63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J63" s="447" t="n">
+      <x:c r="J63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K63" s="447" t="n">
+      <x:c r="K63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L63" s="447" t="n">
+      <x:c r="L63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M63" s="447" t="n">
+      <x:c r="M63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N63" s="447" t="n">
+      <x:c r="N63" s="595" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O63" s="448" t="n">
+      <x:c r="O63" s="596" t="n">
         <x:f>SUM(C63:N63)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P63" s="448" t="n">
+      <x:c r="P63" s="596" t="n">
         <x:f>P135</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="Q63" s="448" t="n">
+      <x:c r="Q63" s="596" t="n">
         <x:f>Q135</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="R63" s="448" t="n">
+      <x:c r="R63" s="596" t="n">
         <x:f>R135</x:f>
         <x:v>24</x:v>
       </x:c>
@@ -5843,24 +6373,24 @@
       <x:c r="B64" s="199"/>
       <x:c r="C64" s="227"/>
       <x:c r="D64" s="227"/>
-      <x:c r="E64" s="435" t="str">
+      <x:c r="E64" s="583" t="str">
         <x:v>Costos unitarios trazables</x:v>
       </x:c>
-      <x:c r="F64" s="436"/>
-      <x:c r="G64" s="437"/>
+      <x:c r="F64" s="584"/>
+      <x:c r="G64" s="585"/>
       <x:c r="H64" s="227"/>
       <x:c r="I64" s="227"/>
-      <x:c r="J64" s="435" t="str">
+      <x:c r="J64" s="583" t="str">
         <x:v>Importación simplificada por kit</x:v>
       </x:c>
-      <x:c r="K64" s="436"/>
-      <x:c r="L64" s="437"/>
+      <x:c r="K64" s="584"/>
+      <x:c r="L64" s="585"/>
       <x:c r="M64" s="227"/>
-      <x:c r="N64" s="435" t="str">
+      <x:c r="N64" s="583" t="str">
         <x:v>Consultas especializadas</x:v>
       </x:c>
-      <x:c r="O64" s="436"/>
-      <x:c r="P64" s="437"/>
+      <x:c r="O64" s="584"/>
+      <x:c r="P64" s="585"/>
       <x:c r="Q64" s="228"/>
       <x:c r="R64" s="229"/>
     </x:row>
@@ -5871,7 +6401,7 @@
       <x:c r="B65" s="196" t="str">
         <x:v>unidades</x:v>
       </x:c>
-      <x:c r="C65" s="428" t="n">
+      <x:c r="C65" s="576" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D65" s="208"/>
@@ -5881,7 +6411,7 @@
       <x:c r="F65" s="308" t="str">
         <x:v>USD/u</x:v>
       </x:c>
-      <x:c r="G65" s="440" t="n">
+      <x:c r="G65" s="588" t="n">
         <x:v>49.3</x:v>
       </x:c>
       <x:c r="H65" s="208"/>
@@ -5903,7 +6433,7 @@
       <x:c r="O65" s="323" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="P65" s="445" t="n">
+      <x:c r="P65" s="593" t="n">
         <x:v>3000</x:v>
       </x:c>
       <x:c r="Q65" s="226"/>
@@ -5927,7 +6457,7 @@
       <x:c r="F66" s="308" t="str">
         <x:v>min/u</x:v>
       </x:c>
-      <x:c r="G66" s="441" t="n">
+      <x:c r="G66" s="589" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H66" s="208"/>
@@ -5949,7 +6479,7 @@
       <x:c r="O66" s="323" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="P66" s="445" t="n">
+      <x:c r="P66" s="593" t="n">
         <x:v>2500</x:v>
       </x:c>
       <x:c r="Q66" s="226"/>
@@ -5973,7 +6503,7 @@
       <x:c r="F67" s="308" t="str">
         <x:v>min/u</x:v>
       </x:c>
-      <x:c r="G67" s="441" t="n">
+      <x:c r="G67" s="589" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H67" s="208"/>
@@ -5995,7 +6525,7 @@
       <x:c r="O67" s="323" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="P67" s="445" t="n">
+      <x:c r="P67" s="593" t="n">
         <x:v>3500</x:v>
       </x:c>
       <x:c r="Q67" s="226"/>
@@ -6008,7 +6538,7 @@
       <x:c r="B68" s="196" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="C68" s="429" t="n">
+      <x:c r="C68" s="577" t="n">
         <x:v>300</x:v>
       </x:c>
       <x:c r="D68" s="208"/>
@@ -6018,7 +6548,7 @@
       <x:c r="F68" s="308" t="str">
         <x:v>min/u</x:v>
       </x:c>
-      <x:c r="G68" s="441" t="n">
+      <x:c r="G68" s="589" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H68" s="208"/>
@@ -6029,7 +6559,7 @@
       <x:c r="K68" s="308" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="L68" s="440" t="n">
+      <x:c r="L68" s="588" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="M68" s="208"/>
@@ -6039,7 +6569,7 @@
       <x:c r="O68" s="323" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="P68" s="445" t="n">
+      <x:c r="P68" s="593" t="n">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="Q68" s="226"/>
@@ -6063,7 +6593,7 @@
       <x:c r="F69" s="308" t="str">
         <x:v>min/u</x:v>
       </x:c>
-      <x:c r="G69" s="441" t="n">
+      <x:c r="G69" s="589" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H69" s="208"/>
@@ -6074,7 +6604,7 @@
       <x:c r="K69" s="308" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="L69" s="440" t="n">
+      <x:c r="L69" s="588" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="M69" s="208"/>
@@ -6098,7 +6628,7 @@
       <x:c r="B70" s="196" t="str">
         <x:v>USD/parche</x:v>
       </x:c>
-      <x:c r="C70" s="429" t="n">
+      <x:c r="C70" s="577" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D70" s="208"/>
@@ -6160,7 +6690,7 @@
       <x:c r="K71" s="308" t="str">
         <x:v>% CIF</x:v>
       </x:c>
-      <x:c r="L71" s="443" t="n">
+      <x:c r="L71" s="591" t="n">
         <x:v>0.16</x:v>
       </x:c>
       <x:c r="M71" s="208"/>
@@ -6187,7 +6717,7 @@
       <x:c r="F72" s="308" t="str">
         <x:v>USD/u</x:v>
       </x:c>
-      <x:c r="G72" s="440" t="n">
+      <x:c r="G72" s="588" t="n">
         <x:v>26.65</x:v>
       </x:c>
       <x:c r="H72" s="208"/>
@@ -6198,7 +6728,7 @@
       <x:c r="K72" s="308" t="str">
         <x:v>% CIF</x:v>
       </x:c>
-      <x:c r="L72" s="443" t="n">
+      <x:c r="L72" s="591" t="n">
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="M72" s="208"/>
@@ -6225,7 +6755,7 @@
       <x:c r="F73" s="308" t="str">
         <x:v>min/u</x:v>
       </x:c>
-      <x:c r="G73" s="441" t="n">
+      <x:c r="G73" s="589" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H73" s="208"/>
@@ -6236,7 +6766,7 @@
       <x:c r="K73" s="308" t="str">
         <x:v>% CIF</x:v>
       </x:c>
-      <x:c r="L73" s="443" t="n">
+      <x:c r="L73" s="591" t="n">
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="M73" s="208"/>
@@ -6263,7 +6793,7 @@
       <x:c r="F74" s="308" t="str">
         <x:v>min/u</x:v>
       </x:c>
-      <x:c r="G74" s="441" t="n">
+      <x:c r="G74" s="589" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H74" s="208"/>
@@ -6302,7 +6832,7 @@
       <x:c r="F75" s="308" t="str">
         <x:v>min/u</x:v>
       </x:c>
-      <x:c r="G75" s="441" t="n">
+      <x:c r="G75" s="589" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H75" s="208"/>
@@ -6313,7 +6843,7 @@
       <x:c r="K75" s="308" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="L75" s="440" t="n">
+      <x:c r="L75" s="588" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="M75" s="208"/>
@@ -6340,7 +6870,7 @@
       <x:c r="F76" s="308" t="str">
         <x:v>min/u</x:v>
       </x:c>
-      <x:c r="G76" s="441" t="n">
+      <x:c r="G76" s="589" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H76" s="208"/>
@@ -6351,7 +6881,7 @@
       <x:c r="K76" s="308" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="L76" s="440" t="n">
+      <x:c r="L76" s="588" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="M76" s="208"/>
@@ -6390,7 +6920,7 @@
       <x:c r="K77" s="308" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="L77" s="440" t="n">
+      <x:c r="L77" s="588" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="M77" s="208"/>
@@ -6458,7 +6988,7 @@
       <x:c r="F79" s="308" t="str">
         <x:v>USD/u</x:v>
       </x:c>
-      <x:c r="G79" s="440" t="n">
+      <x:c r="G79" s="588" t="n">
         <x:v>7.25</x:v>
       </x:c>
       <x:c r="H79" s="208"/>
@@ -6498,7 +7028,7 @@
       <x:c r="F80" s="308" t="str">
         <x:v>h/100 u</x:v>
       </x:c>
-      <x:c r="G80" s="440" t="n">
+      <x:c r="G80" s="588" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="H80" s="208"/>
@@ -6576,11 +7106,11 @@
       </x:c>
       <x:c r="H82" s="208"/>
       <x:c r="I82" s="208"/>
-      <x:c r="J82" s="435" t="str">
+      <x:c r="J82" s="583" t="str">
         <x:v>Preserie año 1 sin doble mano de obra</x:v>
       </x:c>
-      <x:c r="K82" s="436"/>
-      <x:c r="L82" s="437"/>
+      <x:c r="K82" s="584"/>
+      <x:c r="L82" s="585"/>
       <x:c r="M82" s="208"/>
       <x:c r="N82" s="208"/>
       <x:c r="O82" s="226"/>
@@ -6605,7 +7135,7 @@
       <x:c r="F83" s="308" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="G83" s="440" t="n">
+      <x:c r="G83" s="588" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H83" s="208"/>
@@ -6644,7 +7174,7 @@
       <x:c r="F84" s="308" t="str">
         <x:v>USD/kit</x:v>
       </x:c>
-      <x:c r="G84" s="440" t="n">
+      <x:c r="G84" s="588" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H84" s="208"/>
@@ -6784,20 +7314,20 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="D88" s="208"/>
-      <x:c r="E88" s="435" t="str">
+      <x:c r="E88" s="583" t="str">
         <x:v>Criterios de costeo e importación</x:v>
       </x:c>
-      <x:c r="F88" s="436"/>
-      <x:c r="G88" s="436"/>
-      <x:c r="H88" s="436"/>
-      <x:c r="I88" s="436"/>
-      <x:c r="J88" s="436"/>
-      <x:c r="K88" s="436"/>
-      <x:c r="L88" s="436"/>
-      <x:c r="M88" s="436"/>
-      <x:c r="N88" s="436"/>
-      <x:c r="O88" s="436"/>
-      <x:c r="P88" s="437"/>
+      <x:c r="F88" s="584"/>
+      <x:c r="G88" s="584"/>
+      <x:c r="H88" s="584"/>
+      <x:c r="I88" s="584"/>
+      <x:c r="J88" s="584"/>
+      <x:c r="K88" s="584"/>
+      <x:c r="L88" s="584"/>
+      <x:c r="M88" s="584"/>
+      <x:c r="N88" s="584"/>
+      <x:c r="O88" s="584"/>
+      <x:c r="P88" s="585"/>
       <x:c r="Q88" s="226"/>
       <x:c r="R88" s="226"/>
     </x:row>
@@ -8497,7 +9027,7 @@
         <x:v>Origen temporal de cálculo</x:v>
       </x:c>
       <x:c r="B154" s="196"/>
-      <x:c r="C154" s="243" t="n">
+      <x:c r="C154" s="526" t="n">
         <x:f>DATE(2027,1,1)</x:f>
         <x:v>46388</x:v>
       </x:c>
@@ -8766,8 +9296,8 @@
       <x:c r="E166" s="232" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F166" s="244" t="n">
-        <x:f t="shared" ref="F166:F181" si="79">$C$154</x:f>
+      <x:c r="F166" s="526" t="n">
+        <x:f t="shared" ref="F166:F181" si="79">$C$154+ROUND(E166*365/12,0)</x:f>
         <x:v>46388</x:v>
       </x:c>
       <x:c r="G166" s="246" t="n">
@@ -8794,7 +9324,7 @@
       <x:c r="E167" s="232" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F167" s="244" t="n">
+      <x:c r="F167" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E167*365/12,0)</x:f>
         <x:v>46418</x:v>
       </x:c>
@@ -8822,7 +9352,7 @@
       <x:c r="E168" s="232" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F168" s="244" t="n">
+      <x:c r="F168" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E168*365/12,0)</x:f>
         <x:v>46449</x:v>
       </x:c>
@@ -8850,7 +9380,7 @@
       <x:c r="E169" s="232" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F169" s="244" t="n">
+      <x:c r="F169" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E169*365/12,0)</x:f>
         <x:v>46479</x:v>
       </x:c>
@@ -8878,7 +9408,7 @@
       <x:c r="E170" s="232" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F170" s="244" t="n">
+      <x:c r="F170" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E170*365/12,0)</x:f>
         <x:v>46510</x:v>
       </x:c>
@@ -8906,7 +9436,7 @@
       <x:c r="E171" s="232" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F171" s="244" t="n">
+      <x:c r="F171" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E171*365/12,0)</x:f>
         <x:v>46540</x:v>
       </x:c>
@@ -8934,7 +9464,7 @@
       <x:c r="E172" s="232" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F172" s="244" t="n">
+      <x:c r="F172" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E172*365/12,0)</x:f>
         <x:v>46571</x:v>
       </x:c>
@@ -8962,7 +9492,7 @@
       <x:c r="E173" s="232" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F173" s="244" t="n">
+      <x:c r="F173" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E173*365/12,0)</x:f>
         <x:v>46601</x:v>
       </x:c>
@@ -8990,7 +9520,7 @@
       <x:c r="E174" s="232" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F174" s="244" t="n">
+      <x:c r="F174" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E174*365/12,0)</x:f>
         <x:v>46631</x:v>
       </x:c>
@@ -9018,7 +9548,7 @@
       <x:c r="E175" s="232" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F175" s="244" t="n">
+      <x:c r="F175" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E175*365/12,0)</x:f>
         <x:v>46662</x:v>
       </x:c>
@@ -9046,7 +9576,7 @@
       <x:c r="E176" s="232" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F176" s="244" t="n">
+      <x:c r="F176" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E176*365/12,0)</x:f>
         <x:v>46692</x:v>
       </x:c>
@@ -9074,7 +9604,7 @@
       <x:c r="E177" s="232" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F177" s="244" t="n">
+      <x:c r="F177" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E177*365/12,0)</x:f>
         <x:v>46723</x:v>
       </x:c>
@@ -9102,7 +9632,7 @@
       <x:c r="E178" s="232" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F178" s="244" t="n">
+      <x:c r="F178" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E178*365/12,0)</x:f>
         <x:v>46753</x:v>
       </x:c>
@@ -9130,7 +9660,7 @@
       <x:c r="E179" s="232" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F179" s="244" t="n">
+      <x:c r="F179" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E179*365/12,0)</x:f>
         <x:v>47118</x:v>
       </x:c>
@@ -9158,7 +9688,7 @@
       <x:c r="E180" s="232" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F180" s="244" t="n">
+      <x:c r="F180" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E180*365/12,0)</x:f>
         <x:v>47483</x:v>
       </x:c>
@@ -9186,7 +9716,7 @@
       <x:c r="E181" s="232" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F181" s="244" t="n">
+      <x:c r="F181" s="526" t="n">
         <x:f t="shared" si="79">$C$154+ROUND(E181*365/12,0)</x:f>
         <x:v>47848</x:v>
       </x:c>
@@ -12644,9 +13174,9 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf99cefe441194293"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dfd1cb5c6234013"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29be34b19bbc45c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4bf07b3e0804053"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14633,30 +15163,30 @@
       <x:c r="V51" s="271"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="435" t="str">
+      <x:c r="A54" s="583" t="str">
         <x:v>Años 2 a 4: Kanban comercial/operativo y objetivos trimestrales</x:v>
       </x:c>
-      <x:c r="B54" s="436"/>
-      <x:c r="C54" s="436"/>
-      <x:c r="D54" s="436"/>
-      <x:c r="E54" s="436"/>
-      <x:c r="F54" s="436"/>
-      <x:c r="G54" s="436"/>
-      <x:c r="H54" s="436"/>
-      <x:c r="I54" s="436"/>
-      <x:c r="J54" s="436"/>
-      <x:c r="K54" s="436"/>
-      <x:c r="L54" s="436"/>
-      <x:c r="M54" s="436"/>
-      <x:c r="N54" s="436"/>
-      <x:c r="O54" s="436"/>
-      <x:c r="P54" s="436"/>
-      <x:c r="Q54" s="436"/>
-      <x:c r="R54" s="436"/>
-      <x:c r="S54" s="436"/>
-      <x:c r="T54" s="436"/>
-      <x:c r="U54" s="436"/>
-      <x:c r="V54" s="437"/>
+      <x:c r="B54" s="584"/>
+      <x:c r="C54" s="584"/>
+      <x:c r="D54" s="584"/>
+      <x:c r="E54" s="584"/>
+      <x:c r="F54" s="584"/>
+      <x:c r="G54" s="584"/>
+      <x:c r="H54" s="584"/>
+      <x:c r="I54" s="584"/>
+      <x:c r="J54" s="584"/>
+      <x:c r="K54" s="584"/>
+      <x:c r="L54" s="584"/>
+      <x:c r="M54" s="584"/>
+      <x:c r="N54" s="584"/>
+      <x:c r="O54" s="584"/>
+      <x:c r="P54" s="584"/>
+      <x:c r="Q54" s="584"/>
+      <x:c r="R54" s="584"/>
+      <x:c r="S54" s="584"/>
+      <x:c r="T54" s="584"/>
+      <x:c r="U54" s="584"/>
+      <x:c r="V54" s="585"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="369" t="str">
@@ -14709,16 +15239,16 @@
       <x:c r="V56" s="367"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="435" t="str">
+      <x:c r="A57" s="583" t="str">
         <x:v>Columnas del tablero Kanban</x:v>
       </x:c>
-      <x:c r="B57" s="436"/>
-      <x:c r="C57" s="436"/>
-      <x:c r="D57" s="436"/>
-      <x:c r="E57" s="436"/>
-      <x:c r="F57" s="436"/>
-      <x:c r="G57" s="436"/>
-      <x:c r="H57" s="437"/>
+      <x:c r="B57" s="584"/>
+      <x:c r="C57" s="584"/>
+      <x:c r="D57" s="584"/>
+      <x:c r="E57" s="584"/>
+      <x:c r="F57" s="584"/>
+      <x:c r="G57" s="584"/>
+      <x:c r="H57" s="585"/>
       <x:c r="I57" s="367"/>
       <x:c r="J57" s="367"/>
       <x:c r="K57" s="367"/>
@@ -14735,28 +15265,28 @@
       <x:c r="V57" s="367"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="454" t="str">
+      <x:c r="A58" s="602" t="str">
         <x:v>Backlog</x:v>
       </x:c>
-      <x:c r="B58" s="454" t="str">
+      <x:c r="B58" s="602" t="str">
         <x:v>Prospectado</x:v>
       </x:c>
-      <x:c r="C58" s="454" t="str">
+      <x:c r="C58" s="602" t="str">
         <x:v>Contactado</x:v>
       </x:c>
-      <x:c r="D58" s="454" t="str">
+      <x:c r="D58" s="602" t="str">
         <x:v>Reunión</x:v>
       </x:c>
-      <x:c r="E58" s="454" t="str">
+      <x:c r="E58" s="602" t="str">
         <x:v>Acuerdo</x:v>
       </x:c>
-      <x:c r="F58" s="454" t="str">
+      <x:c r="F58" s="602" t="str">
         <x:v>Onboarding</x:v>
       </x:c>
-      <x:c r="G58" s="454" t="str">
+      <x:c r="G58" s="602" t="str">
         <x:v>Aliado activo</x:v>
       </x:c>
-      <x:c r="H58" s="454" t="str">
+      <x:c r="H58" s="602" t="str">
         <x:v>Seguimiento</x:v>
       </x:c>
       <x:c r="I58" s="367"/>
@@ -14825,13 +15355,13 @@
       <x:c r="V60" s="367"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="435" t="str">
+      <x:c r="A61" s="583" t="str">
         <x:v>Frentes paralelos</x:v>
       </x:c>
-      <x:c r="B61" s="436"/>
-      <x:c r="C61" s="436"/>
-      <x:c r="D61" s="436"/>
-      <x:c r="E61" s="437"/>
+      <x:c r="B61" s="584"/>
+      <x:c r="C61" s="584"/>
+      <x:c r="D61" s="584"/>
+      <x:c r="E61" s="585"/>
       <x:c r="F61" s="367"/>
       <x:c r="G61" s="367"/>
       <x:c r="H61" s="367"/>
@@ -14851,19 +15381,19 @@
       <x:c r="V61" s="367"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="454" t="str">
+      <x:c r="A62" s="602" t="str">
         <x:v>Frente</x:v>
       </x:c>
-      <x:c r="B62" s="454" t="str">
+      <x:c r="B62" s="602" t="str">
         <x:v>Objetivo</x:v>
       </x:c>
-      <x:c r="C62" s="454" t="str">
+      <x:c r="C62" s="602" t="str">
         <x:v>Indicador</x:v>
       </x:c>
-      <x:c r="D62" s="454" t="str">
+      <x:c r="D62" s="602" t="str">
         <x:v>Cadencia</x:v>
       </x:c>
-      <x:c r="E62" s="454" t="str">
+      <x:c r="E62" s="602" t="str">
         <x:v>Responsable</x:v>
       </x:c>
       <x:c r="F62" s="367"/>
@@ -15147,17 +15677,17 @@
       <x:c r="V70" s="367"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="435" t="str">
+      <x:c r="A71" s="583" t="str">
         <x:v>Metas trimestrales vinculadas al escenario activo</x:v>
       </x:c>
-      <x:c r="B71" s="436"/>
-      <x:c r="C71" s="436"/>
-      <x:c r="D71" s="436"/>
-      <x:c r="E71" s="436"/>
-      <x:c r="F71" s="436"/>
-      <x:c r="G71" s="436"/>
-      <x:c r="H71" s="436"/>
-      <x:c r="I71" s="437"/>
+      <x:c r="B71" s="584"/>
+      <x:c r="C71" s="584"/>
+      <x:c r="D71" s="584"/>
+      <x:c r="E71" s="584"/>
+      <x:c r="F71" s="584"/>
+      <x:c r="G71" s="584"/>
+      <x:c r="H71" s="584"/>
+      <x:c r="I71" s="585"/>
       <x:c r="J71" s="367"/>
       <x:c r="K71" s="367"/>
       <x:c r="L71" s="367"/>
@@ -15173,31 +15703,31 @@
       <x:c r="V71" s="367"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="454" t="str">
+      <x:c r="A72" s="602" t="str">
         <x:v>Año</x:v>
       </x:c>
-      <x:c r="B72" s="454" t="str">
+      <x:c r="B72" s="602" t="str">
         <x:v>Trimestre</x:v>
       </x:c>
-      <x:c r="C72" s="454" t="str">
+      <x:c r="C72" s="602" t="str">
         <x:v>Aliados acumulados</x:v>
       </x:c>
-      <x:c r="D72" s="454" t="str">
+      <x:c r="D72" s="602" t="str">
         <x:v>Ventas de kits</x:v>
       </x:c>
-      <x:c r="E72" s="454" t="str">
+      <x:c r="E72" s="602" t="str">
         <x:v>Producción bruta</x:v>
       </x:c>
-      <x:c r="F72" s="454" t="str">
+      <x:c r="F72" s="602" t="str">
         <x:v>Demostradores</x:v>
       </x:c>
-      <x:c r="G72" s="454" t="str">
+      <x:c r="G72" s="602" t="str">
         <x:v>Retención</x:v>
       </x:c>
-      <x:c r="H72" s="454" t="str">
+      <x:c r="H72" s="602" t="str">
         <x:v>Soporte (h)</x:v>
       </x:c>
-      <x:c r="I72" s="454" t="str">
+      <x:c r="I72" s="602" t="str">
         <x:v>Criterio de cierre</x:v>
       </x:c>
       <x:c r="J72" s="367"/>
@@ -16547,63 +17077,63 @@
       <x:c r="E49" s="91"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="435" t="str">
+      <x:c r="A52" s="583" t="str">
         <x:v>Canales de adquisición y costos de activación</x:v>
       </x:c>
-      <x:c r="B52" s="436"/>
-      <x:c r="C52" s="436"/>
-      <x:c r="D52" s="436"/>
-      <x:c r="E52" s="437"/>
+      <x:c r="B52" s="584"/>
+      <x:c r="C52" s="584"/>
+      <x:c r="D52" s="584"/>
+      <x:c r="E52" s="585"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="454" t="str">
+      <x:c r="A53" s="602" t="str">
         <x:v>Driver</x:v>
       </x:c>
-      <x:c r="B53" s="454" t="str">
+      <x:c r="B53" s="602" t="str">
         <x:v>Tarifa / criterio</x:v>
       </x:c>
-      <x:c r="C53" s="454" t="str">
+      <x:c r="C53" s="602" t="str">
         <x:v>Año 2</x:v>
       </x:c>
-      <x:c r="D53" s="454" t="str">
+      <x:c r="D53" s="602" t="str">
         <x:v>Año 3</x:v>
       </x:c>
-      <x:c r="E53" s="454" t="str">
+      <x:c r="E53" s="602" t="str">
         <x:v>Año 4</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="455" t="str">
+      <x:c r="A54" s="603" t="str">
         <x:v>Médicos aliados - selección activa</x:v>
       </x:c>
-      <x:c r="B54" s="455"/>
-      <x:c r="C54" s="455" t="n">
+      <x:c r="B54" s="603"/>
+      <x:c r="C54" s="603" t="n">
         <x:f>ROUND(C7*C56/(C56+C57),0)</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D54" s="455" t="n">
+      <x:c r="D54" s="603" t="n">
         <x:f>ROUND(D7*D56/(D56+D57),0)</x:f>
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E54" s="455" t="n">
+      <x:c r="E54" s="603" t="n">
         <x:f>ROUND(E7*E56/(E56+E57),0)</x:f>
         <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="455" t="str">
+      <x:c r="A55" s="603" t="str">
         <x:v>Clínicas aliadas - selección activa</x:v>
       </x:c>
-      <x:c r="B55" s="455"/>
-      <x:c r="C55" s="455" t="n">
+      <x:c r="B55" s="603"/>
+      <x:c r="C55" s="603" t="n">
         <x:f>C7-C54</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D55" s="455" t="n">
+      <x:c r="D55" s="603" t="n">
         <x:f>D7-D54</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E55" s="455" t="n">
+      <x:c r="E55" s="603" t="n">
         <x:f>E7-E54</x:f>
         <x:v>24</x:v>
       </x:c>
@@ -16613,13 +17143,13 @@
         <x:v>Médicos aliados - base aprobada</x:v>
       </x:c>
       <x:c r="B56" s="349"/>
-      <x:c r="C56" s="459" t="n">
+      <x:c r="C56" s="607" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D56" s="459" t="n">
+      <x:c r="D56" s="607" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E56" s="459" t="n">
+      <x:c r="E56" s="607" t="n">
         <x:v>56</x:v>
       </x:c>
     </x:row>
@@ -16628,13 +17158,13 @@
         <x:v>Clínicas aliadas - base aprobada</x:v>
       </x:c>
       <x:c r="B57" s="349"/>
-      <x:c r="C57" s="459" t="n">
+      <x:c r="C57" s="607" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D57" s="459" t="n">
+      <x:c r="D57" s="607" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E57" s="459" t="n">
+      <x:c r="E57" s="607" t="n">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -16661,13 +17191,13 @@
         <x:v>Conversión de prospectos médicos</x:v>
       </x:c>
       <x:c r="B59" s="349"/>
-      <x:c r="C59" s="460" t="n">
+      <x:c r="C59" s="608" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="D59" s="460" t="n">
+      <x:c r="D59" s="608" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="E59" s="460" t="n">
+      <x:c r="E59" s="608" t="n">
         <x:v>0.2</x:v>
       </x:c>
     </x:row>
@@ -16694,13 +17224,13 @@
         <x:v>Conversión de prospectos de clínicas</x:v>
       </x:c>
       <x:c r="B61" s="349"/>
-      <x:c r="C61" s="460" t="n">
+      <x:c r="C61" s="608" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="D61" s="460" t="n">
+      <x:c r="D61" s="608" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="E61" s="460" t="n">
+      <x:c r="E61" s="608" t="n">
         <x:v>0.2</x:v>
       </x:c>
     </x:row>
@@ -16726,7 +17256,7 @@
       <x:c r="A63" s="349" t="str">
         <x:v>Onboarding de médicos (USD)</x:v>
       </x:c>
-      <x:c r="B63" s="461" t="n">
+      <x:c r="B63" s="609" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="C63" s="358" t="n">
@@ -16746,7 +17276,7 @@
       <x:c r="A64" s="349" t="str">
         <x:v>Onboarding de clínicas (USD)</x:v>
       </x:c>
-      <x:c r="B64" s="461" t="n">
+      <x:c r="B64" s="609" t="n">
         <x:v>300</x:v>
       </x:c>
       <x:c r="C64" s="358" t="n">
@@ -16763,19 +17293,19 @@
       </x:c>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="457" t="str">
+      <x:c r="A65" s="605" t="str">
         <x:v>Onboarding total (USD)</x:v>
       </x:c>
-      <x:c r="B65" s="462"/>
-      <x:c r="C65" s="462" t="n">
+      <x:c r="B65" s="610"/>
+      <x:c r="C65" s="610" t="n">
         <x:f>SUM(C63:C64)</x:f>
         <x:v>3450</x:v>
       </x:c>
-      <x:c r="D65" s="462" t="n">
+      <x:c r="D65" s="610" t="n">
         <x:f>SUM(D63:D64)</x:f>
         <x:v>7125</x:v>
       </x:c>
-      <x:c r="E65" s="462" t="n">
+      <x:c r="E65" s="610" t="n">
         <x:f>SUM(E63:E64)</x:f>
         <x:v>11400</x:v>
       </x:c>
@@ -16788,28 +17318,28 @@
       <x:c r="E66" s="367"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="435" t="str">
+      <x:c r="A67" s="583" t="str">
         <x:v>Acciones del canal</x:v>
       </x:c>
-      <x:c r="B67" s="436"/>
-      <x:c r="C67" s="436"/>
-      <x:c r="D67" s="436"/>
-      <x:c r="E67" s="437"/>
+      <x:c r="B67" s="584"/>
+      <x:c r="C67" s="584"/>
+      <x:c r="D67" s="584"/>
+      <x:c r="E67" s="585"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="454" t="str">
+      <x:c r="A68" s="602" t="str">
         <x:v>Etapa</x:v>
       </x:c>
-      <x:c r="B68" s="454" t="str">
+      <x:c r="B68" s="602" t="str">
         <x:v>Evidencia de cierre</x:v>
       </x:c>
-      <x:c r="C68" s="454" t="str">
+      <x:c r="C68" s="602" t="str">
         <x:v>Médicos</x:v>
       </x:c>
-      <x:c r="D68" s="454" t="str">
+      <x:c r="D68" s="602" t="str">
         <x:v>Clínicas</x:v>
       </x:c>
-      <x:c r="E68" s="454" t="str">
+      <x:c r="E68" s="602" t="str">
         <x:v>Responsable</x:v>
       </x:c>
     </x:row>
@@ -16940,13 +17470,13 @@
       <x:c r="E76" s="367"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="435" t="str">
+      <x:c r="A77" s="583" t="str">
         <x:v>Notas del canal</x:v>
       </x:c>
-      <x:c r="B77" s="436"/>
-      <x:c r="C77" s="436"/>
-      <x:c r="D77" s="436"/>
-      <x:c r="E77" s="437"/>
+      <x:c r="B77" s="584"/>
+      <x:c r="C77" s="584"/>
+      <x:c r="D77" s="584"/>
+      <x:c r="E77" s="585"/>
     </x:row>
     <x:row r="78" ht="24" customHeight="1">
       <x:c r="A78" s="368" t="str">
@@ -17011,20 +17541,20 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="466" t="str">
+      <x:c r="A1" s="614" t="str">
         <x:v>Cambios realizados — corrección integral</x:v>
       </x:c>
-      <x:c r="B1" s="466"/>
-      <x:c r="C1" s="466"/>
-      <x:c r="D1" s="466"/>
+      <x:c r="B1" s="614"/>
+      <x:c r="C1" s="614"/>
+      <x:c r="D1" s="614"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="476" t="str">
+      <x:c r="A2" s="623" t="str">
         <x:v>Resumen informativo. La hoja Flujo de caja sigue siendo la fuente financiera autoritativa.</x:v>
       </x:c>
-      <x:c r="B2" s="476"/>
-      <x:c r="C2" s="476"/>
-      <x:c r="D2" s="476"/>
+      <x:c r="B2" s="623"/>
+      <x:c r="C2" s="623"/>
+      <x:c r="D2" s="623"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="367"/>
@@ -17033,21 +17563,21 @@
       <x:c r="D3" s="367"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="454" t="str">
+      <x:c r="A4" s="602" t="str">
         <x:v>Área</x:v>
       </x:c>
-      <x:c r="B4" s="454" t="str">
+      <x:c r="B4" s="602" t="str">
         <x:v>Cambio realizado</x:v>
       </x:c>
-      <x:c r="C4" s="454" t="str">
+      <x:c r="C4" s="602" t="str">
         <x:v>Resultado final</x:v>
       </x:c>
-      <x:c r="D4" s="454" t="str">
+      <x:c r="D4" s="602" t="str">
         <x:v>Evidencia en el libro</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="38" customHeight="1">
-      <x:c r="A5" s="471" t="str">
+      <x:c r="A5" s="619" t="str">
         <x:v>Planificación</x:v>
       </x:c>
       <x:c r="B5" s="360" t="str">
@@ -17061,7 +17591,7 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
-      <x:c r="A6" s="471" t="str">
+      <x:c r="A6" s="619" t="str">
         <x:v>Alcance</x:v>
       </x:c>
       <x:c r="B6" s="360" t="str">
@@ -17075,7 +17605,7 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
-      <x:c r="A7" s="471" t="str">
+      <x:c r="A7" s="619" t="str">
         <x:v>FODA y riesgos</x:v>
       </x:c>
       <x:c r="B7" s="360" t="str">
@@ -17089,7 +17619,7 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="38" customHeight="1">
-      <x:c r="A8" s="471" t="str">
+      <x:c r="A8" s="619" t="str">
         <x:v>Costeo</x:v>
       </x:c>
       <x:c r="B8" s="360" t="str">
@@ -17103,7 +17633,7 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="38" customHeight="1">
-      <x:c r="A9" s="471" t="str">
+      <x:c r="A9" s="619" t="str">
         <x:v>Preserie año 1</x:v>
       </x:c>
       <x:c r="B9" s="360" t="str">
@@ -17117,7 +17647,7 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="38" customHeight="1">
-      <x:c r="A10" s="471" t="str">
+      <x:c r="A10" s="619" t="str">
         <x:v>Importación</x:v>
       </x:c>
       <x:c r="B10" s="360" t="str">
@@ -17131,7 +17661,7 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="38" customHeight="1">
-      <x:c r="A11" s="471" t="str">
+      <x:c r="A11" s="619" t="str">
         <x:v>Modelo comercial</x:v>
       </x:c>
       <x:c r="B11" s="360" t="str">
@@ -17145,7 +17675,7 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="38" customHeight="1">
-      <x:c r="A12" s="471" t="str">
+      <x:c r="A12" s="619" t="str">
         <x:v>Canales</x:v>
       </x:c>
       <x:c r="B12" s="360" t="str">
@@ -17159,7 +17689,7 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
-      <x:c r="A13" s="471" t="str">
+      <x:c r="A13" s="619" t="str">
         <x:v>Año 1</x:v>
       </x:c>
       <x:c r="B13" s="360" t="str">
@@ -17173,7 +17703,7 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="38" customHeight="1">
-      <x:c r="A14" s="471" t="str">
+      <x:c r="A14" s="619" t="str">
         <x:v>Viabilidad</x:v>
       </x:c>
       <x:c r="B14" s="360" t="str">
@@ -17187,24 +17717,32 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="38" customHeight="1">
-      <x:c r="A15" s="473" t="str">
+      <x:c r="A15" s="621" t="str">
         <x:v>Verificación</x:v>
       </x:c>
-      <x:c r="B15" s="474" t="str">
+      <x:c r="B15" s="622" t="str">
         <x:v>Se probaron escenarios y sensibilidades y se restauró el caso base.</x:v>
       </x:c>
-      <x:c r="C15" s="474" t="str">
+      <x:c r="C15" s="622" t="str">
         <x:v>0 errores de fórmula</x:v>
       </x:c>
-      <x:c r="D15" s="474" t="str">
+      <x:c r="D15" s="622" t="str">
         <x:v>Escaneo del libro y matriz de trazabilidad</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="367"/>
-      <x:c r="B16" s="367"/>
-      <x:c r="C16" s="367"/>
-      <x:c r="D16" s="367"/>
+    <x:row r="16" ht="38" customHeight="1">
+      <x:c r="A16" s="621" t="str">
+        <x:v>Compatibilidad</x:v>
+      </x:c>
+      <x:c r="B16" s="622" t="str">
+        <x:v>Se normalizaron las fechas financieras para Excel y Google Sheets.</x:v>
+      </x:c>
+      <x:c r="C16" s="622" t="str">
+        <x:v>Fechas diferenciadas · formato dd/mm/aaaa · XIRR con estimación inicial</x:v>
+      </x:c>
+      <x:c r="D16" s="622" t="str">
+        <x:v>Flujo de caja · filas 153–181</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="477" t="str">
